--- a/linkedin_fixed_27APR2026.xlsx
+++ b/linkedin_fixed_27APR2026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X67"/>
+  <dimension ref="A1:X69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -596,12 +596,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1,415,139</t>
+          <t>1,415,145</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/emirates-nbd_financialwellbeing-emiratesnbd-investsmart-activity-7454016414891421697-19Wl?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFEqwA4BdvloIrWTBN4Zlcbb4DJ_6CUegWU</t>
+          <t>https://www.linkedin.com/posts/emirates-nbd_financialwellbeing-emiratesnbd-investsmart-activity-7454016414891421697-19Wl?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFEESewBAMg3p8sO1wE0IHk5sJeOLIUEs18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ENBD_C</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -675,7 +675,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/dr-amr-elhorbaty_firstabrbank-emiratesndb-snb-activity-7454279249961578496-JJ4D?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADR2tr0BSG8tIEQfMMtX8P1rjBuxrA1SAiM</t>
+          <t>https://www.linkedin.com/posts/dr-amr-elhorbaty_firstabrbank-emiratesndb-snb-activity-7454279249961578496-JJ4D?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADWSnOwBbh89_Aj3cpE2GunPIETu5GxYt5c</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -781,7 +781,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -826,7 +826,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/blacktop-real-estate_dubai-has-made-off-plan-investing-more-structured-activity-7454259415765102592-Pyf_?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADR2tr0BSG8tIEQfMMtX8P1rjBuxrA1SAiM</t>
+          <t>https://www.linkedin.com/posts/blacktop-real-estate_dubai-has-made-off-plan-investing-more-structured-activity-7454259415765102592-Pyf_?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADWSnOwBbh89_Aj3cpE2GunPIETu5GxYt5c</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -900,7 +900,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -943,12 +943,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>727</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/scientific-gate-company_scientificgateabregypt-mdeabrmansoura-digitaldentistry-activity-7454227815106789377-31SK?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADR2tr0BSG8tIEQfMMtX8P1rjBuxrA1SAiM</t>
+          <t>https://www.linkedin.com/posts/scientific-gate-company_scientificgateabregypt-mdeabrmansoura-digitaldentistry-activity-7454227815106789377-31SK?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADWSnOwBbh89_Aj3cpE2GunPIETu5GxYt5c</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1022,7 +1022,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/mohamed-youssef-47166a278_im-currently-open-to-new-opportunities-in-activity-7454225345765060608-e-Pd?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADR2tr0BSG8tIEQfMMtX8P1rjBuxrA1SAiM</t>
+          <t>https://www.linkedin.com/posts/mohamed-youssef-47166a278_im-currently-open-to-new-opportunities-in-activity-7454225345765060608-e-Pd?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADWSnOwBbh89_Aj3cpE2GunPIETu5GxYt5c</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1132,7 +1132,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/abdelalim-hegazy-8262b2176_excellence-in-performance-and-teamwork-activity-7454214315257126912-MhA3?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADR2tr0BSG8tIEQfMMtX8P1rjBuxrA1SAiM</t>
+          <t>https://www.linkedin.com/posts/abdelalim-hegazy-8262b2176_excellence-in-performance-and-teamwork-activity-7454214315257126912-MhA3?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADWSnOwBbh89_Aj3cpE2GunPIETu5GxYt5c</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1239,7 +1239,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/minaal-s-kurup-05565095_enbd-gemsaward-topperformer-activity-7454130703035850752-gvqz?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADR2tr0BSG8tIEQfMMtX8P1rjBuxrA1SAiM</t>
+          <t>https://www.linkedin.com/posts/minaal-s-kurup-05565095_enbd-gemsaward-topperformer-activity-7454130703035850752-gvqz?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADWSnOwBbh89_Aj3cpE2GunPIETu5GxYt5c</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1349,7 +1349,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/activity-7454130676997713921-v3Op?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADR2tr0BSG8tIEQfMMtX8P1rjBuxrA1SAiM</t>
+          <t>https://www.linkedin.com/posts/activity-7454130676997713921-v3Op?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADWSnOwBbh89_Aj3cpE2GunPIETu5GxYt5c</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1458,7 +1458,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/kayanleadership_aeraeyaepaeuabraepaesaeqaeyaepaexaepaes-aetaebaeyaezaerabraetaevaeuaeyaer-activity-7454127144533708800-rk2Y?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADR2tr0BSG8tIEQfMMtX8P1rjBuxrA1SAiM</t>
+          <t>https://www.linkedin.com/posts/kayanleadership_aeraeyaepaeuabraepaesaeqaeyaepaexaepaes-aetaebaeyaezaerabraetaevaeuaeyaer-activity-7454127144533708800-rk2Y?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADWSnOwBbh89_Aj3cpE2GunPIETu5GxYt5c</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1584,7 +1584,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/mohamed-youssef-47166a278_im-currently-open-to-new-opportunities-in-activity-7454225234452373504-7xW4?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADR2tr0BSG8tIEQfMMtX8P1rjBuxrA1SAiM</t>
+          <t>https://www.linkedin.com/posts/mohamed-youssef-47166a278_im-currently-open-to-new-opportunities-in-activity-7454225234452373504-7xW4?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADWSnOwBbh89_Aj3cpE2GunPIETu5GxYt5c</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1693,7 +1693,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>128</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/talentbridge0_financialcrimecompliance-aml-datagovernance-activity-7454122359634063360-m2dt?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADR2tr0BSG8tIEQfMMtX8P1rjBuxrA1SAiM</t>
+          <t>https://www.linkedin.com/posts/talentbridge0_financialcrimecompliance-aml-datagovernance-activity-7454122359634063360-m2dt?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADWSnOwBbh89_Aj3cpE2GunPIETu5GxYt5c</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1809,7 +1809,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/asmarealestate_dubairealestate-offplan-investment-activity-7454113065135984640-U6Dq?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADUz8rgBNXHbch_tvy2RkhT4zrbn1VGFYNs</t>
+          <t>https://www.linkedin.com/posts/asmarealestate_dubairealestate-offplan-investment-activity-7454113065135984640-U6Dq?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEk8-z0B7dM2q5buqGHbCZriZXOx2kEtc08</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1933,7 +1933,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/thevakul_corporategovernance-mergersandacquisitions-activity-7454094570281283585-29kd?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADUz8rgBNXHbch_tvy2RkhT4zrbn1VGFYNs</t>
+          <t>https://www.linkedin.com/posts/thevakul_corporategovernance-mergersandacquisitions-activity-7454094570281283585-29kd?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEk8-z0B7dM2q5buqGHbCZriZXOx2kEtc08</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2049,7 +2049,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/mahra-alhammadi-333453257_%D8%A3%D8%B9%D9%84%D9%86-%D8%B9%D9%86-%D8%A3%D9%86%D9%86%D9%8A-%D9%85%D8%AA%D8%A7%D8%AD%D8%A9-%D8%AD%D8%A7%D9%84%D9%8A%D8%A7-%D9%84%D9%81%D8%B1%D8%B5-%D8%B9%D9%85%D9%84-%D8%A8%D8%AF%D9%88%D8%A7%D9%85-activity-7454088590244032514-XQyY?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADUz8rgBNXHbch_tvy2RkhT4zrbn1VGFYNs</t>
+          <t>https://www.linkedin.com/posts/mahra-alhammadi-333453257_%D8%A3%D8%B9%D9%84%D9%86-%D8%B9%D9%86-%D8%A3%D9%86%D9%86%D9%8A-%D9%85%D8%AA%D8%A7%D8%AD%D8%A9-%D8%AD%D8%A7%D9%84%D9%8A%D8%A7-%D9%84%D9%81%D8%B1%D8%B5-%D8%B9%D9%85%D9%84-%D8%A8%D8%AF%D9%88%D8%A7%D9%85-activity-7454088590244032514-XQyY?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEk8-z0B7dM2q5buqGHbCZriZXOx2kEtc08</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2160,7 +2160,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/a2properties_dubairealestate-dubaiproperty-offplandubai-activity-7454078466481852416-mbzk?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADUz8rgBNXHbch_tvy2RkhT4zrbn1VGFYNs</t>
+          <t>https://www.linkedin.com/posts/a2properties_dubairealestate-dubaiproperty-offplandubai-activity-7454078466481852416-mbzk?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEk8-z0B7dM2q5buqGHbCZriZXOx2kEtc08</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2278,7 +2278,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" t="n">
         <v>4</v>
@@ -2326,7 +2326,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/%D9%90abdo-mohsen159_all-the-details-about-me-activity-7454073533015658496-1ZVY?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADUz8rgBNXHbch_tvy2RkhT4zrbn1VGFYNs</t>
+          <t>https://www.linkedin.com/posts/%D9%90abdo-mohsen159_all-the-details-about-me-activity-7454073533015658496-1ZVY?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEk8-z0B7dM2q5buqGHbCZriZXOx2kEtc08</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2400,7 +2400,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/kerolos-sameh-227a18215_bankers-loan-the-best-rate-in-the-market-activity-7454061787479543808-4gcw?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADUz8rgBNXHbch_tvy2RkhT4zrbn1VGFYNs</t>
+          <t>https://www.linkedin.com/posts/kerolos-sameh-227a18215_bankers-loan-the-best-rate-in-the-market-activity-7454061787479543808-4gcw?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEk8-z0B7dM2q5buqGHbCZriZXOx2kEtc08</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2549,7 +2549,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/nour-mostafa-elsamaloty-080547250_bankersabrloan-aeqaeuaer-aeqaeuaer-activity-7454061231461744640-vTD6?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADUz8rgBNXHbch_tvy2RkhT4zrbn1VGFYNs</t>
+          <t>https://www.linkedin.com/posts/nour-mostafa-elsamaloty-080547250_bankersabrloan-aeqaeuaer-aeqaeuaer-activity-7454061231461744640-vTD6?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEk8-z0B7dM2q5buqGHbCZriZXOx2kEtc08</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2702,7 +2702,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/zetbankerae_best-personal-loans-uae-for-expats-2026-activity-7454059405269979136-D_oJ?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADUz8rgBNXHbch_tvy2RkhT4zrbn1VGFYNs</t>
+          <t>https://www.linkedin.com/posts/zetbankerae_best-personal-loans-uae-for-expats-2026-activity-7454059405269979136-D_oJ?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEk8-z0B7dM2q5buqGHbCZriZXOx2kEtc08</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2831,7 +2831,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/uae-fintechvibes_digitalwallet-uaefintech-adgm-activity-7454046660650844160-DGqo?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADUz8rgBNXHbch_tvy2RkhT4zrbn1VGFYNs</t>
+          <t>https://www.linkedin.com/posts/uae-fintechvibes_digitalwallet-uaefintech-adgm-activity-7454046660650844160-DGqo?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEk8-z0B7dM2q5buqGHbCZriZXOx2kEtc08</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2949,17 +2949,241 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Prime Financial Hub</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46139.33341012731</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Get filtered &amp; verified loan and credit card leads matched to your exact banking criteria.
+✔ Higher approval ratios
+ ✔ Ready-to-convert prospects
+ ✔ Consistent daily lead flow
+📩 Message now  WhatsApp 055 669 5602   
+#primefinancialhub #BankingLeads #LoanLeads #CreditCardLeads #FinancialServices #BankingSales #LeadGeneration #HighQualityLeads #VerifiedLeads #SalesGrowth #BankingProfessionals #FinanceIndustry #PersonalLoan #CreditCards #UAEFinance #SalesLeads #B2BLeads #LeadGenerationServices #ConversionFocused #SalesStrategy #BusinessGrowth #DirectSales #TargetedLeads #BulkData #CallCenterLeads #IncreaseSales #primeleads #enbd #cbd #rak #mashreq #fab #eib #dib #adib</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/prime-financial-hub_primefinancialhub-bankingleads-loanleads-activity-7454378821199290368-sLWs?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAD8de6QBbUfVkcN4vN1HrYGOj5BhYtUL0fw</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7454378821199290368</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>ENBD1</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>get filtered &amp; verified loan and credit card leads matched to your exact banking criteria. higher approval ratios ready-to-convert prospects consistent daily lead flow message now whatsapp 055 669 5602 #primefinancialhub #bankingleads #loanleads #creditcardleads #financialservices #bankingsales #leadgeneration #highqualityleads #verifiedleads #salesgrowth #bankingprofessionals #financeindustry #personalloan #creditcards #uaefinance #salesleads #b2bleads #leadgenerationservices #conversionfocused #salesstrategy #businessgrowth #directsales #targetedleads #bulkdata #callcenterleads #increasesales #primeleads #enbd #cbd #rak #mashreq #fab #eib #dib #adib</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Prime Financial Hub</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>get filtered &amp; verified loan and credit card leads matched to your exact banking criteria. higher approval ratios ready-to-convert prospects consistent daily lead flow message now whatsapp 055 669 5602 #primefinancialhub #bankingleads #loanleads #creditcardleads #financialservices #bankingsales #leadgeneration #highqualityleads #verifiedleads #salesgrowth #bankingprofessionals #financeindustry #personalloan #creditcards #uaefinance #salesleads #b2bleads #leadgenerationservices #conversionfocused #salesstrategy #businessgrowth #directsales #targetedleads #bulkdata #callcenterleads #increasesales #primeleads #enbd #cbd #rak #mashreq #fab #eib #dib #adib</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>21</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>get filtered &amp; verified loan and credit card leads matched to your exact banking criteria.</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>27-04-2026</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Esports News Bangladesh</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46139.31541065972</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>🔴 𝗖𝗢𝗠𝗠𝗨𝗡𝗜𝗧𝗬 𝗠𝗘𝗦𝗦𝗔𝗚𝗘 — 𝗞𝗨𝗧𝗧𝗨𝗦𝗛 🗣️
+RHK - KUTTUSH এর স্টেটমেন্ট আমরা ন্যাশনালে তেমন একটা Sniper এর অভাব বুঝি না তবু নিজের সবটা দিয়ে সাপোটার থেকে বেকবন হিসেবে নিজেকে রেডি করবো দেখার বিষয় কেমন হয় এবার RHK ❤️‍🩹
+#rhk #kuttush #ENBD 
+#ENewsBD #FreeFireEsportsBd</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/esports-news-bangladesh-631954404_rhk-kuttush-enbd-activity-7454372298410688512-BamS?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAD8de6QBbUfVkcN4vN1HrYGOj5BhYtUL0fw</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7454372298410688512</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>ENBD1</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>— rhk - kuttush এর স্টেটমেন্ট আমরা ন্যাশনালে তেমন একটা sniper এর অভাব বুঝি না তবু নিজের সবটা দিয়ে সাপোটার থেকে বেকবন হিসেবে নিজেকে রেডি করবো দেখার বিষয় কেমন হয় এবার rhk ‍ #rhk #kuttush #enbd #enewsbd #freefireesportsbd</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Esports News Bangladesh</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>— rhk - kuttush এর স্টেটমেন্ট আমরা ন্যাশনালে তেমন একটা sniper এর অভাব বুঝি না তবু নিজের সবটা দিয়ে সাপোটার থেকে বেকবন হিসেবে নিজেকে রেডি করবো দেখার বিষয় কেমন হয় এবার rhk ‍ #rhk #kuttush #enbd #enewsbd #freefireesportsbd</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>22</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>— rhk - kuttush এর স্টেটমেন্ট আমরা ন্যাশনালে তেমন একটা sniper এর অভাব বুঝি না তবু নিজের সবটা দিয়ে সাপোটার থেকে বেকবন হিস…</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>27-04-2026</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Muthu Krishnan A N</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C24" s="2" t="n">
         <v>46138.96676372685</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>https://lnkd.in/g5MKzt7R
 RBL Bank Q4 FY26 Results :
@@ -2982,108 +3206,108 @@
 #RBLBank #ApnoKaBank #BoldNewRBLBank #SubramaniakumarR #JaideepIyer</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E24" t="n">
         <v>3</v>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/muthu-krishnan-a-n-54ba21185_rblbank-apnokabank-boldnewrblbank-activity-7454245952993005569-tcZ0?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADVQx30BSKw-4RPuvwIzJnoG8AqJtvBc4vY</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/muthu-krishnan-a-n-54ba21185_rblbank-apnokabank-boldnewrblbank-activity-7454245952993005569-tcZ0?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAD8de6QBbUfVkcN4vN1HrYGOj5BhYtUL0fw</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>urn:li:activity:7454245952993005569</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>ENBD1</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>rbl bank q4 fy26 results : balance sheet : rs 2,53,250 crs fy26 vs rs.2,03,562 crs fy25 net profit : 822 crs fy26 ( yoy growth 18% ) total deposits : rs.1,39,018 crs ( 25% yoy growth ) total advances : rs.1,14,232 crs (23% yoy growth) granular deposits ( &lt; 3 crs ) grew by 16% yoy to rs.63,943 crs , constituting 65% of the total deposit book. retail and wholesale advance mix - 59:41 secured retail advance disbursement rs.18,500 crs fy 26 vs rs.10,400 crs fy25 wholesale banking advance grew by 28% yoy casa ratio : 33.6 % cd ratio : 82.2% average lcr 130% gross npa 1.45% fy26 ( 2.6% fy25) total capital adequacy ratio : 14.25 % , cet1 12.8% rating upgrade on the cards post enbd capital infusion transaction. enbd transaction expected this quarter. branch network will be added by 150 to 200 branches in fy27. overall bank had a good growth in deposits , advances , assets quality and the bottom line net profit in fy26. #rblbank #apnokabank #boldnewrblbank #subramaniakumarr #jaideepiyer</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Muthu Krishnan A N</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>rbl bank q4 fy26 results : balance sheet : rs 2,53,250 crs fy26 vs rs.2,03,562 crs fy25 net profit : 822 crs fy26 ( yoy growth 18% ) total deposits : rs.1,39,018 crs ( 25% yoy growth ) total advances : rs.1,14,232 crs (23% yoy growth) granular deposits ( &lt; 3 crs ) grew by 16% yoy to rs.63,943 crs , constituting 65% of the total deposit book. retail and wholesale advance mix - 59:41 secured retail advance disbursement rs.18,500 crs fy 26 vs rs.10,400 crs fy25 wholesale banking advance grew by 28% yoy casa ratio : 33.6 % cd ratio : 82.2% average lcr 130% gross npa 1.45% fy26 ( 2.6% fy25) total capital adequacy ratio : 14.25 % , cet1 12.8% rating upgrade on the cards post enbd capital infusion transaction. enbd transaction expected this quarter. branch network will be added by 150 to 200 branches in fy27. overall bank had a good growth in deposits , advances , assets quality and the bottom line net profit in fy26. #rblbank #apnokabank #boldnewrblbank #subramaniakumarr #jaideepiyer</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R22" t="n">
-        <v>21</v>
-      </c>
-      <c r="S22" t="inlineStr">
+      <c r="R24" t="n">
+        <v>23</v>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>overall bank had a good growth in deposits , advances , assets quality and the bottom line net profit in fy26. • branch network will be added by 150 to 200 branches in fy27. • enbd transaction expected this quarter.</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
+    <row r="25">
+      <c r="A25" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Redwan Y. Anbarseri</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C25" s="2" t="n">
         <v>46138.79145034722</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Pleased to see this achievement recognized.
 Having worked with Senior RM Ahmed Helmy Wahdan , I can attest to his strong commitment, professionalism, and dedication to delivering value to our ENBD clients.
@@ -3092,215 +3316,215 @@
 #business_banking_growth_innovation</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E25" t="n">
         <v>5</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F25" t="n">
         <v>2</v>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/redwan-y-anbarseri-4268bb167_emiratesabrnbdabrksa-bestabrsmeabrbankabrmiddleabreast-activity-7454182421551300608-xu-L?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADVQx30BSKw-4RPuvwIzJnoG8AqJtvBc4vY</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/redwan-y-anbarseri-4268bb167_emiratesabrnbdabrksa-bestabrsmeabrbankabrmiddleabreast-activity-7454182421551300608-xu-L?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAD8de6QBbUfVkcN4vN1HrYGOj5BhYtUL0fw</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>urn:li:activity:7454182421551300608</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>ENBD1</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>pleased to see this achievement recognized. having worked with senior rm ahmed helmy wahdan , i can attest to his strong commitment, professionalism, and dedication to delivering value to our enbd clients. a well-deserved milestone wishing him continued success ahead. #emirates_nbd_ksa #business_banking_growth_innovation</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Redwan Y. Anbarseri</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>pleased to see this achievement recognized. having worked with senior rm ahmed helmy wahdan , i can attest to his strong commitment, professionalism, and dedication to delivering value to our enbd clients. a well-deserved milestone wishing him continued success ahead. #emirates_nbd_ksa #business_banking_growth_innovation</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R23" t="n">
-        <v>22</v>
-      </c>
-      <c r="S23" t="inlineStr">
+      <c r="R25" t="n">
+        <v>24</v>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>having worked with senior rm ahmed helmy wahdan , i can attest to his strong commitment, professionalism, and dedication to delivering value to our enbd clients. • a well-deserved milestone wishing him continued success ahead. • #emirates_nbd_ksa #business_banking_growth_innovation</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
+    <row r="26">
+      <c r="A26" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Vivek Kar</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C26" s="2" t="n">
         <v>46138.51899731482</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Strong start to 2026 with a profit before tax of AED 8.2 billion and and 6% year-on-year growth, reflecting sustained momentum across the UAE banking sector.
 #enbd #dubai</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E26" t="n">
         <v>1</v>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/vivek-kar_q1-2026-financial-results-activity-7454083687878467584-UWqx?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADVQx30BSKw-4RPuvwIzJnoG8AqJtvBc4vY</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/vivek-kar_q1-2026-financial-results-activity-7454083687878467584-UWqx?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAD8de6QBbUfVkcN4vN1HrYGOj5BhYtUL0fw</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>urn:li:activity:7454083687878467584</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>ENBD1</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>strong start to 2026 with a profit before tax of aed 8.2 billion and and 6% year-on-year growth, reflecting sustained momentum across the uae banking sector. #enbd #dubai</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Vivek Kar</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>strong start to 2026 with a profit before tax of aed 8.2 billion and and 6% year-on-year growth, reflecting sustained momentum across the uae banking sector. #enbd #dubai</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R24" t="n">
-        <v>23</v>
-      </c>
-      <c r="S24" t="inlineStr">
+      <c r="R26" t="n">
+        <v>25</v>
+      </c>
+      <c r="S26" t="inlineStr">
         <is>
           <t>strong start to 2026 with a profit before tax of aed 8.2 billion and and 6% year-on-year growth, reflecting sustained momentum across the uae banking sector.</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
+    <row r="27">
+      <c r="A27" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Emirates Islamic</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C27" s="2" t="n">
         <v>46138.58335104166</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>كل استثمارهو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق.
 #الإمارات_الإسلامي #الخدمات_المصرفية_المميزة #الخدمات_المصرفية_في_الإمارات #بنك_الإمارات_الإسلامي
@@ -3310,112 +3534,112 @@
 https://lnkd.in/dTSgJs8p</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E27" t="n">
         <v>7</v>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>383,968</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/emirates-islamic-bank_aepaesaenaetaepaezaepaesabraepaesaenaebaesaepaetaey-activity-7454107008888352768-g4pw?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAER_BBABGhA9dGZybaazDxY9GE7jgGPFMtc</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>383,969</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/emirates-islamic-bank_aepaesaenaetaepaezaepaesabraepaesaenaebaesaepaetaey-activity-7454107008888352768-g4pw?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADgkugABfTvu1Oqvu9fKf-ocJ-ZlwKbSxgA</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>urn:li:activity:7454107008888352768</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>EI_C</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>كل استثمارهو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق. #الإمارات_الإسلامي #الخدمات_المصرفية_المميزة #الخدمات_المصرفية_في_الإمارات #بنك_الإمارات_الإسلامي  every financial journey deserves personal attention. from your first investment to building generational wealth, emirates islamic priority banking is by your side. discover the difference today. #emiratesislamic #prioritybanking #uaebanking #emiratesislamicbank</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Emirates Islamic</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>كل استثمارهو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق. #الإمارات_الإسلامي #الخدمات_المصرفية_المميزة #الخدمات_المصرفية_في_الإمارات #بنك_الإمارات_الإسلامي  every financial journey deserves personal attention. from your first investment to building generational wealth, emirates islamic priority banking is by your side. discover the difference today. #emiratesislamic #prioritybanking #uaebanking #emiratesislamicbank</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R25" t="n">
-        <v>24</v>
-      </c>
-      <c r="S25" t="inlineStr">
+      <c r="R27" t="n">
+        <v>26</v>
+      </c>
+      <c r="S27" t="inlineStr">
         <is>
           <t>from your first investment to building generational wealth, emirates islamic priority banking is by your side. • #الإمارات_الإسلامي #الخدمات_المصرفية_المميزة #الخدمات_المصرفية_في_الإمارات #بنك_الإمارات_الإسلامي every financial journey deserves personal attention. • #emiratesislamic #prioritybanking #uaebanking #emiratesislamicbank</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
+    <row r="28">
+      <c r="A28" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Emirates Islamic</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C28" s="2" t="n">
         <v>46138.54168003472</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Scale new heights with an expected profit rate of up to 6.00% p.a. with the Emirates Islamic e-Savings Account. Simply follow the below steps:
 ⭐️ Open an Emirates Islamic e-Savings Account
@@ -3426,285 +3650,63 @@
 Terms &amp; Conditions apply.</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E28" t="n">
         <v>1</v>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>383,968</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/emirates-islamic-bank_scale-new-heights-with-an-expected-profit-activity-7454091907821060096-fOy2?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAER_BBABGhA9dGZybaazDxY9GE7jgGPFMtc</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>383,969</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/emirates-islamic-bank_scale-new-heights-with-an-expected-profit-activity-7454091907821060096-fOy2?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADgkugABfTvu1Oqvu9fKf-ocJ-ZlwKbSxgA</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>urn:li:activity:7454091907821060096</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>EI_C</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>scale new heights with an expected profit rate of up to 6.00% p.a. with the emirates islamic e-savings account. simply follow the below steps: open an emirates islamic e-savings account deposit aed 50,000 and above in the e-saving account offer valid from 1 february till 30 april 2026. to know more, visit  terms &amp; conditions apply.</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Emirates Islamic</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>scale new heights with an expected profit rate of up to 6.00% p.a. with the emirates islamic e-savings account. simply follow the below steps: open an emirates islamic e-savings account deposit aed 50,000 and above in the e-saving account offer valid from 1 february till 30 april 2026. to know more, visit  terms &amp; conditions apply.</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Positive</t>
-        </is>
-      </c>
-      <c r="R26" t="n">
-        <v>25</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>simply follow the below steps: open an emirates islamic e-savings account deposit aed 50,000 and above in the e-saving account offer valid from 1 february till 30 april 2026. • scale new heights with an expected profit rate of up to 6.00% p.a. • with the emirates islamic e-savings account.</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>26-04-2026</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Emirates Islamic</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>46138.50001150463</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
-Download the EI + Mobile Banking App today.</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>linkedinVideo</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>383,968</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/emirates-islamic-bank_digital-wealth-account-opening-activity-7454076807651287041-jTVc?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAER_BBABGhA9dGZybaazDxY9GE7jgGPFMtc</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>urn:li:activity:7454076807651287041</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>EI_C</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>open a digital wealth account instantly to enjoy a complete suite of shariah-compliant global investments. get access to international &amp; uae stocks as well as global mutual funds. download the ei + mobile banking app today.</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Emirates Islamic</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>open a digital wealth account instantly to enjoy a complete suite of shariah-compliant global investments. get access to international &amp; uae stocks as well as global mutual funds. download the ei + mobile banking app today.</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="R27" t="n">
-        <v>26</v>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>open a digital wealth account instantly to enjoy a complete suite of shariah-compliant global investments. • get access to international &amp; uae stocks as well as global mutual funds. • download the ei + mobile banking app today.</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>26-04-2026</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Emirates Islamic</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>46138.50001075232</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
-قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>linkedinVideo</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>383,968</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/emirates-islamic-bank_digital-wealth-account-opening-activity-7454076807378743297-l0w3?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAER_BBABGhA9dGZybaazDxY9GE7jgGPFMtc</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>urn:li:activity:7454076807378743297</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>EI_C</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية. قم بتحميل تطبيق + ei للخدمات المصرفية عبر الهاتف المتحرك.</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Emirates Islamic</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية. قم بتحميل تطبيق + ei للخدمات المصرفية عبر الهاتف المتحرك.</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Neutral</t>
         </is>
       </c>
       <c r="R28" t="n">
@@ -3712,7 +3714,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. • احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية. • قم بتحميل تطبيق + ei للخدمات المصرفية عبر الهاتف المتحرك.</t>
+          <t>simply follow the below steps: open an emirates islamic e-savings account deposit aed 50,000 and above in the e-saving account offer valid from 1 february till 30 april 2026. • scale new heights with an expected profit rate of up to 6.00% p.a. • with the emirates islamic e-savings account.</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -3743,17 +3745,239 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Emirates Islamic</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>46138.50001150463</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>linkedinVideo</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>383,969</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/emirates-islamic-bank_digital-wealth-account-opening-activity-7454076807651287041-jTVc?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADgkugABfTvu1Oqvu9fKf-ocJ-ZlwKbSxgA</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7454076807651287041</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>EI_C</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>open a digital wealth account instantly to enjoy a complete suite of shariah-compliant global investments. get access to international &amp; uae stocks as well as global mutual funds. download the ei + mobile banking app today.</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Emirates Islamic</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>open a digital wealth account instantly to enjoy a complete suite of shariah-compliant global investments. get access to international &amp; uae stocks as well as global mutual funds. download the ei + mobile banking app today.</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>28</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>open a digital wealth account instantly to enjoy a complete suite of shariah-compliant global investments. • get access to international &amp; uae stocks as well as global mutual funds. • download the ei + mobile banking app today.</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>26-04-2026</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Emirates Islamic</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>46138.50001075232</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>linkedinVideo</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>383,969</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/emirates-islamic-bank_digital-wealth-account-opening-activity-7454076807378743297-l0w3?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADgkugABfTvu1Oqvu9fKf-ocJ-ZlwKbSxgA</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7454076807378743297</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>EI_C</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية. قم بتحميل تطبيق + ei للخدمات المصرفية عبر الهاتف المتحرك.</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Emirates Islamic</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية. قم بتحميل تطبيق + ei للخدمات المصرفية عبر الهاتف المتحرك.</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>29</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. • احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية. • قم بتحميل تطبيق + ei للخدمات المصرفية عبر الهاتف المتحرك.</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>26-04-2026</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Emirates Islamic</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C31" s="2" t="n">
         <v>46138.41667520833</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>لا تحتاج إلى معالجة كل شيء دفعة واحدة.
 ابدأ بمصروف رئيسي واحد.
@@ -3762,112 +3986,112 @@
 https://lnkd.in/d9NNbjUm</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E31" t="n">
         <v>1</v>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>383,968</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/emirates-islamic-bank_aeuaegaezaesaerabraepaesaetaepaesaeyaer-aepaesaesaetaeqaeyaepabraepaesaetaepaesaey-activity-7454046607588679680-ZDlm?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAER_BBABGhA9dGZybaazDxY9GE7jgGPFMtc</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>383,969</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/emirates-islamic-bank_aeuaegaezaesaerabraepaesaetaepaesaeyaer-aepaesaesaetaeqaeyaepabraepaesaetaepaesaey-activity-7454046607588679680-ZDlm?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADgkugABfTvu1Oqvu9fKf-ocJ-ZlwKbSxgA</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>urn:li:activity:7454046607588679680</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>EI_C</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>لا تحتاج إلى معالجة كل شيء دفعة واحدة. ابدأ بمصروف رئيسي واحد. الاستمرارية تصنع تقدّماً حقيقياً. #نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Emirates Islamic</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>لا تحتاج إلى معالجة كل شيء دفعة واحدة. ابدأ بمصروف رئيسي واحد. الاستمرارية تصنع تقدّماً حقيقياً. #نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R29" t="n">
-        <v>28</v>
-      </c>
-      <c r="S29" t="inlineStr">
+      <c r="R31" t="n">
+        <v>30</v>
+      </c>
+      <c r="S31" t="inlineStr">
         <is>
           <t>لا تحتاج إلى معالجة كل شيء دفعة واحدة. • الاستمرارية تصنع تقدّماً حقيقياً. • #نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
+    <row r="32">
+      <c r="A32" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Emirates Islamic</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C32" s="2" t="n">
         <v>46138.41667431713</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>You don’t need to fix everything at once.
 Focus on one big expense.
@@ -3876,112 +4100,112 @@
 https://lnkd.in/d49rJ6qG</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>7</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="E32" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>383,968</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/emirates-islamic-bank_eifinancialwellbeing-smartmoneymindset-emiratesislamic-activity-7454046607265820672-NOqY?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAER_BBABGhA9dGZybaazDxY9GE7jgGPFMtc</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>383,969</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/emirates-islamic-bank_eifinancialwellbeing-smartmoneymindset-emiratesislamic-activity-7454046607265820672-NOqY?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADgkugABfTvu1Oqvu9fKf-ocJ-ZlwKbSxgA</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>urn:li:activity:7454046607265820672</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>EI_C</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>you don’t need to fix everything at once. focus on one big expense. consistency creates real progress. #eifinancialwellbeing #smartmoneymindset #emiratesislamic</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Emirates Islamic</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>you don’t need to fix everything at once. focus on one big expense. consistency creates real progress. #eifinancialwellbeing #smartmoneymindset #emiratesislamic</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R30" t="n">
-        <v>29</v>
-      </c>
-      <c r="S30" t="inlineStr">
+      <c r="R32" t="n">
+        <v>31</v>
+      </c>
+      <c r="S32" t="inlineStr">
         <is>
           <t>you don’t need to fix everything at once. • focus on one big expense. • consistency creates real progress.</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
+    <row r="33">
+      <c r="A33" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Brahim Aidara Ndiaye</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C33" s="2" t="n">
         <v>46139.19257107639</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Retour des images 
 *Remerciements officiels à Mme la Mairesse et à son équipe*
@@ -3997,108 +4221,108 @@
 Emirates</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/brahim-aidara-ndiaye-900225175_retour-des-images-remerciements-officiels-activity-7454327782836170752-Iozf?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACkMr30BF7v71j-98q3xU5URz7rvjUb1Qsg</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/brahim-aidara-ndiaye-900225175_retour-des-images-remerciements-officiels-activity-7454327782836170752-Iozf?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACB8EEgBvo4gTi9INeBXV_R6aanhBVcWAiA</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>urn:li:activity:7454327782836170752</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>retour des images *remerciements officiels à mme la mairesse et à son équipe* au nom de notre délégation et en mon nom personnel, je tiens à exprimer mes sincères remerciements à *madame la maraisse de la commune* de golf sud khadija mahecor diouf ainsi qu’à toute son équipe municipale pour l’accueil chaleureux et l’invitation honorifique que vous nous avez réservés lors de la réception de la délégation italienne. votre sens de l’hospitalité, votre engagement pour le dialogue interculturel et votre ouverture à la coopération internationale témoignent d’un leadership exemplaire. khadijamgs tul cette rencontre marque un pas important vers le renforcement des liens entre nos communautés, dans un esprit de *paix, de solidarité et de développement partagé*. *merci pour votre confiance, votre soutien et votre vision inspirante.* *mr brahim aidara ndiaye président de l'association taxawuma assistance handicap des maladies rares du sénégal* emirates islamic emirates</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Brahim Aidara Ndiaye</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>retour des images *remerciements officiels à mme la mairesse et à son équipe* au nom de notre délégation et en mon nom personnel, je tiens à exprimer mes sincères remerciements à *madame la maraisse de la commune* de golf sud khadija mahecor diouf ainsi qu’à toute son équipe municipale pour l’accueil chaleureux et l’invitation honorifique que vous nous avez réservés lors de la réception de la délégation italienne. votre sens de l’hospitalité, votre engagement pour le dialogue interculturel et votre ouverture à la coopération internationale témoignent d’un leadership exemplaire. khadijamgs tul cette rencontre marque un pas important vers le renforcement des liens entre nos communautés, dans un esprit de *paix, de solidarité et de développement partagé*. *merci pour votre confiance, votre soutien et votre vision inspirante.* *mr brahim aidara ndiaye président de l'association taxawuma assistance handicap des maladies rares du sénégal* emirates islamic emirates</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R31" t="n">
-        <v>30</v>
-      </c>
-      <c r="S31" t="inlineStr">
+      <c r="R33" t="n">
+        <v>32</v>
+      </c>
+      <c r="S33" t="inlineStr">
         <is>
           <t>votre sens de l’hospitalité, votre engagement pour le dialogue interculturel et votre ouverture à la coopération internationale témoignent d’un leadership exemplaire. • khadijamgs tul cette rencontre marque un pas important vers le renforcement des liens entre nos communautés, dans un esprit de *paix, de solidarité et de développement partagé*.</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>27-04-2026</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
+    <row r="34">
+      <c r="A34" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Manikandan Sundaram PMP PSM CSPO</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C34" s="2" t="n">
         <v>46139.18751275463</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>🗞️ GCC Banking Tech Roundup — Edition #288 | 27 Apr 2026
  Your crisp daily roundup of top banking-tech developments across the GCC — focused on innovation, AI, and financial transformation.
@@ -4119,108 +4343,108 @@
 #GCCBanking #AIBanking #DigitalTransformation #FintechGCC #SmartBanking #DataDrivenFinance</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E34" t="n">
         <v>1</v>
       </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/manikandansundarampmp_gccbanking-aibanking-digitaltransformation-activity-7454325949761826816-5DFj?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACkMr30BF7v71j-98q3xU5URz7rvjUb1Qsg</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/manikandansundarampmp_gccbanking-aibanking-digitaltransformation-activity-7454325949761826816-5DFj?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACB8EEgBvo4gTi9INeBXV_R6aanhBVcWAiA</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>urn:li:activity:7454325949761826816</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>gcc banking tech roundup — edition #288 | 27 apr 2026 your crisp daily roundup of top banking-tech developments across the gcc — focused on innovation, ai, and financial transformation. uae – emirates islamic: enhances its digital banking platform with ai-driven customer insights and personalized financial recommendations. impact: strengthens engagement through tailored, data-driven banking experiences. ksa – riyad bank: expands its open banking capabilities with advanced api integrations to support fintech collaboration and digital services. impact: accelerates ecosystem innovation and seamless third-party integrations. qatar – commercial bank of dubai: implements ai-based document processing for trade finance to automate verification and reduce manual workflows. impact: improves efficiency and reduces processing turnaround times. bahrain – ila bank: introduces enhanced in-app financial planning tools powered by data analytics and behavioral insights. impact: drives customer retention and promotes better financial decision-making. oman – bankdhofar: upgrades its digital onboarding journey with biometric authentication and ekyc enhancements. impact: simplifies account opening while strengthening compliance and security. kuwait – gulf bank: strengthens its data analytics infrastructure to support real-time risk monitoring and predictive insights. impact: enhances decision-making accuracy and proactive risk management. big picture: data-driven personalization, open banking, and ai-powered automation continue to reshape scalable and intelligent banking ecosystems across the gcc. stay informed. share this update with your gcc banking and fintech network. #gccbanking #aibanking #digitaltransformation #fintechgcc #smartbanking #datadrivenfinance</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Manikandan Sundaram PMP PSM CSPO</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>gcc banking tech roundup — edition #288 | 27 apr 2026 your crisp daily roundup of top banking-tech developments across the gcc — focused on innovation, ai, and financial transformation. uae – emirates islamic: enhances its digital banking platform with ai-driven customer insights and personalized financial recommendations. impact: strengthens engagement through tailored, data-driven banking experiences. ksa – riyad bank: expands its open banking capabilities with advanced api integrations to support fintech collaboration and digital services. impact: accelerates ecosystem innovation and seamless third-party integrations. qatar – commercial bank of dubai: implements ai-based document processing for trade finance to automate verification and reduce manual workflows. impact: improves efficiency and reduces processing turnaround times. bahrain – ila bank: introduces enhanced in-app financial planning tools powered by data analytics and behavioral insights. impact: drives customer retention and promotes better financial decision-making. oman – bankdhofar: upgrades its digital onboarding journey with biometric authentication and ekyc enhancements. impact: simplifies account opening while strengthening compliance and security. kuwait – gulf bank: strengthens its data analytics infrastructure to support real-time risk monitoring and predictive insights. impact: enhances decision-making accuracy and proactive risk management. big picture: data-driven personalization, open banking, and ai-powered automation continue to reshape scalable and intelligent banking ecosystems across the gcc. stay informed. share this update with your gcc banking and fintech network. #gccbanking #aibanking #digitaltransformation #fintechgcc #smartbanking #datadrivenfinance</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R32" t="n">
-        <v>31</v>
-      </c>
-      <c r="S32" t="inlineStr">
+      <c r="R34" t="n">
+        <v>33</v>
+      </c>
+      <c r="S34" t="inlineStr">
         <is>
           <t>gcc banking tech roundup — edition #288 | 27 apr 2026 your crisp daily roundup of top banking-tech developments across the gcc — focused on innovation, ai, and financial transformation. • big picture: data-driven personalization, open banking, and ai-powered automation continue to reshape scalable and intelligent banking ecosystems across the gcc. • uae – emirates islamic: enhances its digital banking platform with ai-driven customer insights and personalized financial recommendations.</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>27-04-2026</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
+    <row r="35">
+      <c r="A35" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Shaymaa Afana</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
+      <c r="C35" s="2" t="n">
         <v>46138.93588565972</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>I am writing to express my interest in any suitable position within your organization related to customer service, administration, or operations.
 With over 6 years of experience in the UAE across banking, customer service, Customer Service | Administrative Supervisor | Banking &amp; Operations | PRO &amp; Government Transactions |  AND UAE Experience , I have developed strong skills in handling customer interactions, resolving issues, and managing office operations efficiently.
@@ -4230,216 +4454,216 @@
 ‏⭐ لقد عملتُ سابقًا في ‏Aafaq Islamic Finance PSC‏.</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E35" t="n">
         <v>3</v>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="inlineStr">
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/shaymaa-afana-887902300_i-am-writing-to-express-my-interest-in-any-activity-7454234763155927040-XLH_?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACkMr30BF7v71j-98q3xU5URz7rvjUb1Qsg</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/shaymaa-afana-887902300_i-am-writing-to-express-my-interest-in-any-activity-7454234763155927040-XLH_?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACB8EEgBvo4gTi9INeBXV_R6aanhBVcWAiA</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>urn:li:activity:7454234763155927040</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>i am writing to express my interest in any suitable position within your organization related to customer service, administration, or operations. with over 6 years of experience in the uae across banking, customer service, customer service | administrative supervisor | banking &amp; operations | pro &amp; government transactions | and uae experience , i have developed strong skills in handling customer interactions, resolving issues, and managing office operations efficiently. معلومات حولي وحول ما أبحث عنه: ‏ أبحث عن وظائف ‏‏مشرف إدارة، المالية، سكرتير تنفيذى، محاسب، و ممثل خدمة العملاء‏‏. ‏ أنا متاح للتواصل بشأن الوظائف في ‏sharjah emirate و ajman‏. ‏ لقد عملتُ سابقًا في ‏aafaq islamic finance psc‏.</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Shaymaa Afana</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>i am writing to express my interest in any suitable position within your organization related to customer service, administration, or operations. with over 6 years of experience in the uae across banking, customer service, customer service | administrative supervisor | banking &amp; operations | pro &amp; government transactions | and uae experience , i have developed strong skills in handling customer interactions, resolving issues, and managing office operations efficiently. معلومات حولي وحول ما أبحث عنه: ‏ أبحث عن وظائف ‏‏مشرف إدارة، المالية، سكرتير تنفيذى، محاسب، و ممثل خدمة العملاء‏‏. ‏ أنا متاح للتواصل بشأن الوظائف في ‏sharjah emirate و ajman‏. ‏ لقد عملتُ سابقًا في ‏aafaq islamic finance psc‏.</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R33" t="n">
-        <v>32</v>
-      </c>
-      <c r="S33" t="inlineStr">
+      <c r="R35" t="n">
+        <v>34</v>
+      </c>
+      <c r="S35" t="inlineStr">
         <is>
           <t>i am writing to express my interest in any suitable position within your organization related to customer service, administration, or operations. • ‏ لقد عملتُ سابقًا في ‏aafaq islamic finance psc‏. • ‏ أنا متاح للتواصل بشأن الوظائف في ‏sharjah emirate و ajman‏.</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B34" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>Omar Farooq</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
+      <c r="C36" s="2" t="n">
         <v>46138.56382896991</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Pleasure meeting SUJITH PILLAI  Head of HR at Marquis Developers.  
 Glad to collaborate through Emirates Islamic’s Employee Banking Program, supporting seamless onboarding and providing tailored banking solutions for all new joiners. Looking forward to strengthening this partnership and delivering added value to employees.
 Emirates Islamic</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>23</v>
-      </c>
-      <c r="F34" t="n">
+      <c r="E36" t="n">
+        <v>26</v>
+      </c>
+      <c r="F36" t="n">
         <v>1</v>
       </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/omar-farooq-94a58b23_pleasure-meeting-sujith-pillai-head-of-hr-activity-7454099934326210560-1dSO?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACkMr30BF7v71j-98q3xU5URz7rvjUb1Qsg</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/omar-farooq-94a58b23_pleasure-meeting-sujith-pillai-head-of-hr-activity-7454099934326210560-1dSO?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACB8EEgBvo4gTi9INeBXV_R6aanhBVcWAiA</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>urn:li:activity:7454099934326210560</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>pleasure meeting sujith pillai head of hr at marquis developers. glad to collaborate through emirates islamic’s employee banking program, supporting seamless onboarding and providing tailored banking solutions for all new joiners. looking forward to strengthening this partnership and delivering added value to employees. emirates islamic</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Omar Farooq</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>pleasure meeting sujith pillai head of hr at marquis developers. glad to collaborate through emirates islamic’s employee banking program, supporting seamless onboarding and providing tailored banking solutions for all new joiners. looking forward to strengthening this partnership and delivering added value to employees. emirates islamic</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R34" t="n">
-        <v>33</v>
-      </c>
-      <c r="S34" t="inlineStr">
+      <c r="R36" t="n">
+        <v>35</v>
+      </c>
+      <c r="S36" t="inlineStr">
         <is>
           <t>glad to collaborate through emirates islamic’s employee banking program, supporting seamless onboarding and providing tailored banking solutions for all new joiners. • looking forward to strengthening this partnership and delivering added value to employees. • pleasure meeting sujith pillai head of hr at marquis developers.</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
+    <row r="37">
+      <c r="A37" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>ADIB - Abu Dhabi Islamic Bank</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
+      <c r="C37" s="2" t="n">
         <v>46138.45868650463</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Enjoy complimentary Takaful coverage when you open a Ghina Savings Account, designed to help protect what matters most, your family’s future.​
 ​
@@ -4448,223 +4672,223 @@
 #ADIB #GhinaSavings #TakafulCoverage</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>14</v>
-      </c>
-      <c r="F35" t="n">
+      <c r="E37" t="n">
+        <v>15</v>
+      </c>
+      <c r="F37" t="n">
         <v>1</v>
       </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>linkedinVideo</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>655,348</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/abu-dhabi-islamic-bank_adib-ghinasavings-takafulcoverage-activity-7454061831972659200-eKWO?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAF_hh6oBq_19x4GqiahguGJs_2JgtdUhQlU</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>655,352</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/abu-dhabi-islamic-bank_adib-ghinasavings-takafulcoverage-activity-7454061831972659200-eKWO?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFla5sYBmTdPb5wrGOGYmNo5mqPWSmve9nY</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>urn:li:activity:7454061831972659200</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>ADIB_C</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>enjoy complimentary takaful coverage when you open a ghina savings account, designed to help protect what matters most, your family’s future.​ ​ t&amp;cs apply.​ ​ #adib #ghinasavings #takafulcoverage</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>ADIB - Abu Dhabi Islamic Bank</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>enjoy complimentary takaful coverage when you open a ghina savings account, designed to help protect what matters most, your family’s future.​ ​ t&amp;cs apply.​ ​ #adib #ghinasavings #takafulcoverage</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R35" t="n">
-        <v>34</v>
-      </c>
-      <c r="S35" t="inlineStr">
+      <c r="R37" t="n">
+        <v>36</v>
+      </c>
+      <c r="S37" t="inlineStr">
         <is>
           <t>enjoy complimentary takaful coverage when you open a ghina savings account, designed to help protect what matters most, your family’s future.​ ​ t&amp;cs apply.​ ​ #adib #ghinasavings #takafulcoverage</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
+    <row r="38">
+      <c r="A38" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Gates Dubai</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C38" s="2" t="n">
         <v>46139.19004854167</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Abu Dhabi Commercial Bank reports 19th consecutive quarter of increased profits.
 https://lnkd.in/g5ZZczPM</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>article</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>127</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/gates-media-fzco_abu-dhabi-commercial-bank-reports-19th-consecutive-activity-7454326868700213248-CDg0?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAABmUPy4Bvq2yamQUO7_QopTa754Qgqdz_T8</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/gates-media-fzco_abu-dhabi-commercial-bank-reports-19th-consecutive-activity-7454326868700213248-CDg0?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAA0t1AkBl7yMCWejN9FBXmG6mFLxJ4pci6o</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>urn:li:activity:7454326868700213248</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>ADCB</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>abu dhabi commercial bank reports 19th consecutive quarter of increased profits.</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Gates Dubai</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>abu dhabi commercial bank reports 19th consecutive quarter of increased profits.</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R36" t="n">
-        <v>35</v>
-      </c>
-      <c r="S36" t="inlineStr">
+      <c r="R38" t="n">
+        <v>37</v>
+      </c>
+      <c r="S38" t="inlineStr">
         <is>
           <t>abu dhabi commercial bank reports 19th consecutive quarter of increased profits.</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>27-04-2026</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>4. Abu Dhabi Commercial Bank (ADCB)</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>Abu Dhabi Commercial Bank (ADCB)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
+    <row r="39">
+      <c r="A39" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Muhammad Waqas, CMA, CSCA, CFE.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="C39" s="2" t="n">
         <v>46138.81389607639</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>One shareholder owns ~60%.
 The rest barely cross 2%.
@@ -4693,108 +4917,108 @@
 #CorporateStrategy #Ownership #CapitalMarkets #Banking #Governance #InvestmentInsights #FinanceLeadership #UAE</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E39" t="n">
         <v>2</v>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/muhammad-waqas-cma-csca-cfe-06520a9b_corporatestrategy-ownership-capitalmarkets-activity-7454190555611357184-uyTS?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAABmUPy4Bvq2yamQUO7_QopTa754Qgqdz_T8</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/muhammad-waqas-cma-csca-cfe-06520a9b_corporatestrategy-ownership-capitalmarkets-activity-7454190555611357184-uyTS?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAA0t1AkBl7yMCWejN9FBXmG6mFLxJ4pci6o</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>urn:li:activity:7454190555611357184</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>ADCB</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>one shareholder owns ~60%. the rest barely cross 2%. at first glance, this looks like just another ownership breakdown. but it actually tells you everything about how abu dhabi commercial bank is run. mubadala investment company holds the majority. and when one shareholder holds that much… strategy is clear decisions are faster direction doesn’t get diluted the rest of the shareholders the vanguard group, blackrock, and others are important, but they don’t really shape the direction. this is where people often get it wrong. they think ownership is just about percentages. but in reality, it’s about influence. some companies are built on balance. others are built on control. this one is clearly the latter. and honestly, neither model is better. it just depends on what the business needs: * speed and alignment * or debate and market discipline for me, this is where finance becomes interesting. because behind every ownership structure, there’s a very deliberate strategic choice. curious to hear your view: would you rather run a company with clear control, or shared influence? #corporatestrategy #ownership #capitalmarkets #banking #governance #investmentinsights #financeleadership #uae</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Muhammad Waqas, CMA, CSCA, CFE.</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>one shareholder owns ~60%. the rest barely cross 2%. at first glance, this looks like just another ownership breakdown. but it actually tells you everything about how abu dhabi commercial bank is run. mubadala investment company holds the majority. and when one shareholder holds that much… strategy is clear decisions are faster direction doesn’t get diluted the rest of the shareholders the vanguard group, blackrock, and others are important, but they don’t really shape the direction. this is where people often get it wrong. they think ownership is just about percentages. but in reality, it’s about influence. some companies are built on balance. others are built on control. this one is clearly the latter. and honestly, neither model is better. it just depends on what the business needs: * speed and alignment * or debate and market discipline for me, this is where finance becomes interesting. because behind every ownership structure, there’s a very deliberate strategic choice. curious to hear your view: would you rather run a company with clear control, or shared influence? #corporatestrategy #ownership #capitalmarkets #banking #governance #investmentinsights #financeleadership #uae</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R37" t="n">
-        <v>36</v>
-      </c>
-      <c r="S37" t="inlineStr">
+      <c r="R39" t="n">
+        <v>38</v>
+      </c>
+      <c r="S39" t="inlineStr">
         <is>
           <t>it just depends on what the business needs: * speed and alignment * or debate and market discipline for me, this is where finance becomes interesting. • curious to hear your view: would you rather run a company with clear control, or shared influence? • at first glance, this looks like just another ownership breakdown.</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>4. Abu Dhabi Commercial Bank (ADCB)</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>Abu Dhabi Commercial Bank (ADCB)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
+    <row r="40">
+      <c r="A40" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Amal Mustafa</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C40" s="2" t="n">
         <v>46138.75285351852</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>From : 01/08/2004
 To: 30/04/2026
@@ -4806,220 +5030,220 @@
 Abu Dhabi Commercial Bank</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>51</v>
-      </c>
-      <c r="F38" t="n">
+      <c r="E40" t="n">
+        <v>60</v>
+      </c>
+      <c r="F40" t="n">
         <v>20</v>
       </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/amal-mustafa-60751335_from-01082004-to-30042026-i-mark-activity-7454168434529124353-Y6ir?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAABmUPy4Bvq2yamQUO7_QopTa754Qgqdz_T8</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/amal-mustafa-60751335_from-01082004-to-30042026-i-mark-activity-7454168434529124353-Y6ir?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAA0t1AkBl7yMCWejN9FBXmG6mFLxJ4pci6o</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>urn:li:activity:7454168434529124353</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>ADCB</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>from : 01/08/2004 to: 30/04/2026 i mark the end of a remarkable 22-year journey with adcb as i officially retire. it’s hard to put into words what this journey has meant to me. adcb has not just been a workplace,it has been a second home. the people, the culture, and the unwavering support made every challenge worthwhile and every success more meaningful. i can confidently say that adcb is one of the best organizations anyone could hope to be part of. i was fortunate to work alongside inspiring leaders and dedicated colleagues who felt more like family. i leave with a heart full of gratitude, pride, and countless cherished memories. thank you to everyone who has been part of this journey. abu dhabi commercial bank</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Amal Mustafa</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>from : 01/08/2004 to: 30/04/2026 i mark the end of a remarkable 22-year journey with adcb as i officially retire. it’s hard to put into words what this journey has meant to me. adcb has not just been a workplace,it has been a second home. the people, the culture, and the unwavering support made every challenge worthwhile and every success more meaningful. i can confidently say that adcb is one of the best organizations anyone could hope to be part of. i was fortunate to work alongside inspiring leaders and dedicated colleagues who felt more like family. i leave with a heart full of gratitude, pride, and countless cherished memories. thank you to everyone who has been part of this journey. abu dhabi commercial bank</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R38" t="n">
-        <v>37</v>
-      </c>
-      <c r="S38" t="inlineStr">
+      <c r="R40" t="n">
+        <v>39</v>
+      </c>
+      <c r="S40" t="inlineStr">
         <is>
           <t>from : 01/08/2004 to: 30/04/2026 i mark the end of a remarkable 22-year journey with adcb as i officially retire. • adcb has not just been a workplace,it has been a second home. • i can confidently say that adcb is one of the best organizations anyone could hope to be part of.</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>4. Abu Dhabi Commercial Bank (ADCB)</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>Abu Dhabi Commercial Bank (ADCB)</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
+    <row r="41">
+      <c r="A41" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Arabian Business Community (ABC GCC)</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
+      <c r="C41" s="2" t="n">
         <v>46138.48960835648</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Abu Dhabi Commercial Bank, a leading UAE banking group, has delivered record profit before tax of AED3.781 billion in Q1’26, up 30% year on year, extending profit growth track record to 19 consecutive quarters.
 Read more on https://lnkd.in/d_9Vj5ea
 #ABCNews #Banking #Growth #Revenue #Profit</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E41" t="n">
         <v>18</v>
       </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr">
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>4,272</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/abc-gcc_abcnews-banking-growth-activity-7454073037676613633-mO0Z?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAABmUPy4Bvq2yamQUO7_QopTa754Qgqdz_T8</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4,276</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/abc-gcc_abcnews-banking-growth-activity-7454073037676613633-mO0Z?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAA0t1AkBl7yMCWejN9FBXmG6mFLxJ4pci6o</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>urn:li:activity:7454073037676613633</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>ADCB</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>abu dhabi commercial bank, a leading uae banking group, has delivered record profit before tax of aed3.781 billion in q1’26, up 30% year on year, extending profit growth track record to 19 consecutive quarters. read more on  #abcnews #banking #growth #revenue #profit</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Arabian Business Community (ABC GCC)</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>abu dhabi commercial bank, a leading uae banking group, has delivered record profit before tax of aed3.781 billion in q1’26, up 30% year on year, extending profit growth track record to 19 consecutive quarters. read more on  #abcnews #banking #growth #revenue #profit</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R39" t="n">
-        <v>38</v>
-      </c>
-      <c r="S39" t="inlineStr">
+      <c r="R41" t="n">
+        <v>40</v>
+      </c>
+      <c r="S41" t="inlineStr">
         <is>
           <t>read more on #abcnews #banking #growth #revenue #profit</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>4. Abu Dhabi Commercial Bank (ADCB)</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>Abu Dhabi Commercial Bank (ADCB)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
+    <row r="42">
+      <c r="A42" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Gates Dubai</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
+      <c r="C42" s="2" t="n">
         <v>46139.18970741898</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>アブダビ商業銀行、19四半期連続の増益
 アブダビ商業銀行（ADCB）は、2026年1～3月期の純利益が33億6,100万AED（およそ1,445億円）だったと発表した。税引き前利益は37億8,100万AED（およそ1,626億円）で、前年同期比30％増となり、19四半期連続の増益を記録した。
@@ -5028,218 +5252,218 @@
 https://lnkd.in/gMsr4rhc</t>
         </is>
       </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="inlineStr">
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>article</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>127</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/gates-media-fzco_%E3%82%A2%E3%83%96%E3%83%80%E3%83%93%E5%95%86%E6%A5%AD%E9%8A%80%E8%A1%8C19%E5%9B%9B%E5%8D%8A%E6%9C%9F%E9%80%A3%E7%B6%9A%E3%81%AE%E5%A2%97%E7%9B%8A-activity-7454326745081753600-rDL3?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAC0JzDIBL1NztyGLeDkT5vdSluBYkXmJ-jI</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/gates-media-fzco_%E3%82%A2%E3%83%96%E3%83%80%E3%83%93%E5%95%86%E6%A5%AD%E9%8A%80%E8%A1%8C19%E5%9B%9B%E5%8D%8A%E6%9C%9F%E9%80%A3%E7%B6%9A%E3%81%AE%E5%A2%97%E7%9B%8A-activity-7454326745081753600-rDL3?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADakrXoBrim-1nfN8DHgk3OR5K8eppodpWY</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>urn:li:activity:7454326745081753600</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>ADCB1</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>19 adcb202613336,100aed1,445378,100aed1,6263019 593,400aed2,5521836219,600aed94425.6 ai28957,000© wam</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Gates Dubai</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>19 adcb202613336,100aed1,445378,100aed1,6263019 593,400aed2,5521836219,600aed94425.6 ai28957,000© wam</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R40" t="n">
-        <v>39</v>
-      </c>
-      <c r="S40" t="inlineStr">
+      <c r="R42" t="n">
+        <v>41</v>
+      </c>
+      <c r="S42" t="inlineStr">
         <is>
           <t>19 adcb202613336,100aed1,445378,100aed1,6263019 593,400aed2,5521836219,600aed94425.6 ai28957,000© wam</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>27-04-2026</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>4. Abu Dhabi Commercial Bank (ADCB)</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>Abu Dhabi Commercial Bank (ADCB)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
+    <row r="43">
+      <c r="A43" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Randa Hadad</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
+      <c r="C43" s="2" t="n">
         <v>46138.79503395833</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>ADCB❤️</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="E43" t="n">
         <v>1</v>
       </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/randa-hadad-5b37b619a_adcb-uaebanks-financialresults-activity-7454183720208629761-Nz-K?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAC0JzDIBL1NztyGLeDkT5vdSluBYkXmJ-jI</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/randa-hadad-5b37b619a_adcb-uaebanks-financialresults-activity-7454183720208629761-Nz-K?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADakrXoBrim-1nfN8DHgk3OR5K8eppodpWY</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>urn:li:activity:7454183720208629761</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>ADCB1</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>adcb</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Randa Hadad</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>adcb</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R41" t="n">
-        <v>40</v>
-      </c>
-      <c r="S41" t="inlineStr">
+      <c r="R43" t="n">
+        <v>42</v>
+      </c>
+      <c r="S43" t="inlineStr">
         <is>
           <t>adcb</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>4. Abu Dhabi Commercial Bank (ADCB)</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>Abu Dhabi Commercial Bank (ADCB)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
+    <row r="44">
+      <c r="A44" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Yasmin Shokri</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
+      <c r="C44" s="2" t="n">
         <v>46138.4652922801</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>- 778 مليون جنيه غرامة على بنك أبوظبي التجاري ADCB#.
 - 1.98 مليار على HSBC# مصر.
@@ -5295,108 +5519,108 @@
 «المركزي» يعزز الرقابة المشددة.. ويفرض غرامات على عدة بنوك | المصري اليوم https://lnkd.in/dGduSNfA</t>
         </is>
       </c>
-      <c r="E42" t="n">
+      <c r="E44" t="n">
         <v>11</v>
       </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
         <v>1</v>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>article</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/activity-7454064225825484800-td7G?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAC0JzDIBL1NztyGLeDkT5vdSluBYkXmJ-jI</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/activity-7454064225825484800-td7G?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADakrXoBrim-1nfN8DHgk3OR5K8eppodpWY</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>urn:li:activity:7454064225825484800</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>ADCB1</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>- 778 مليون جنيه غرامة على بنك أبوظبي التجاري adcb#. - 1.98 مليار على hsbc# مصر. - 1.115 مليار على المصرف المتحد the united# bank. ليه؟ لأنهم ما وجّهوش 25% من قروضهم للمشروعات الصغيرة والمتوسطة. غرامات بالمليارات على بنوك بسبب عدم الالتزام بتمويل المشروعات الصغيرة والمتوسطة الخبر ده مش مجرد أرقام — ده رسالة قوية جدًا عن اتجاه السوق والرقابة في مصر. خلينا نبص للصورة الأكبر: ١- تمويل الـ smes# مش اختيار… ده التزام فعلي لما بنوك كبيرة تتحاسب بأرقام بالمليارات، يبقى واضح إن الموضوع مش توصيات ولا توجيهات عامة و بس ده التزام رقابي بيتراجع كل 3 شهور، وبأثر مالي مباشر على الأرباح. ٢- على جانب إدارة المخاطر، الصورة بقت أكثر صرامة من أي وقت فات اللي ناس كتير مش واخدة بالها منه إن الغرامات دي مش بس ضغط مالي دي ضغط إداري ومهني على قيادات المخاطر داخل البنوك. خصوصًا بعد واقعة فرض عقوبات قدرها مليار جنيه (21 مليون دولار) على "بنك أبوظبي الأول مصر" لمخالفته إصدار تسهيلات ائتمانية لشركة "بلتون القابضة"، استُخدمت في غرض غير المخصص له، ما دفع "المركزي" أيضاً لطلب نقل رئيس مخاطر الائتمان بوحدة البنك الإماراتي في مصر — وده مؤشر مهم جدًا على مستوى الجدية في التطبيق. وده معناه: إدارات المخاطر تحت رقابة مباشرة مؤشرات الالتزام بقت مرتبطة بمصير القيادات أي فجوة تمويل أو عدم التزام ممكن يتحول لمسؤولية إدارية حقيقية زمن "التأجيل" أو "المعالجة لاحقًا" انتهى ببساطة: risk management بقت في قلب المشهد… مش وظيفة مساندة. ٣- فرصة حقيقية لأصحاب المشروعات — لكن للي جاهز فقط اللي عنده مشروع صغير أو متوسط، أو بيفكر يبدأ، لازم يفهم إن الفترة الجاية هتشهد: - برامج تمويل أكتر - تسهيلات أكبر - منافسة بين البنوك على جذب عملاء الـ smes بس التمويل مش هيروح لأي حد… هيروح للي مؤهل. ٤- الجاهزية بقت كلمة السر المشروع اللي عنده: قوائم مالية واضحة تدفقات نقدية مفهومة نموذج عمل واقعي حوكمة وإدارة مالية منضبطة هو اللي هيستفيد من الموجة الجاية. لأن البنوك نفسها بقت تحت ضغط رقابي… فمش هتغامر بتمويل مشروعات غير مؤهلة. رأيي الشخصي: إحنا داخلين على مرحلة "نضج رقابي" حقيقية اللي بيحصل حاليًا مش مجرد تطبيق تعليمات بل ده إعادة تشكيل لسلوك السوق المصرفي بالكامل. - ضغط على البنوك - ضغط على إدارات المخاطر - ضغط على جودة المحافظ الائتمانية - و فرص أكبر لقطاع الـ smes وده في رأيي من أهم التحولات اللي هتأثر على الاقتصاد الحقيقي في مصر خلال السنين الجاية. #esg #sustainability #البنك_المركزي #إدارة_المخاطر #smes #الاقتصاد_المصري #risk_management #تمويل #حوكمة #القطاع_المصرفي «المركزي» يعزز الرقابة المشددة.. ويفرض غرامات على عدة بنوك | المصري اليوم</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Yasmin Shokri</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>- 778 مليون جنيه غرامة على بنك أبوظبي التجاري adcb#. - 1.98 مليار على hsbc# مصر. - 1.115 مليار على المصرف المتحد the united# bank. ليه؟ لأنهم ما وجّهوش 25% من قروضهم للمشروعات الصغيرة والمتوسطة. غرامات بالمليارات على بنوك بسبب عدم الالتزام بتمويل المشروعات الصغيرة والمتوسطة الخبر ده مش مجرد أرقام — ده رسالة قوية جدًا عن اتجاه السوق والرقابة في مصر. خلينا نبص للصورة الأكبر: ١- تمويل الـ smes# مش اختيار… ده التزام فعلي لما بنوك كبيرة تتحاسب بأرقام بالمليارات، يبقى واضح إن الموضوع مش توصيات ولا توجيهات عامة و بس ده التزام رقابي بيتراجع كل 3 شهور، وبأثر مالي مباشر على الأرباح. ٢- على جانب إدارة المخاطر، الصورة بقت أكثر صرامة من أي وقت فات اللي ناس كتير مش واخدة بالها منه إن الغرامات دي مش بس ضغط مالي دي ضغط إداري ومهني على قيادات المخاطر داخل البنوك. خصوصًا بعد واقعة فرض عقوبات قدرها مليار جنيه (21 مليون دولار) على "بنك أبوظبي الأول مصر" لمخالفته إصدار تسهيلات ائتمانية لشركة "بلتون القابضة"، استُخدمت في غرض غير المخصص له، ما دفع "المركزي" أيضاً لطلب نقل رئيس مخاطر الائتمان بوحدة البنك الإماراتي في مصر — وده مؤشر مهم جدًا على مستوى الجدية في التطبيق. وده معناه: إدارات المخاطر تحت رقابة مباشرة مؤشرات الالتزام بقت مرتبطة بمصير القيادات أي فجوة تمويل أو عدم التزام ممكن يتحول لمسؤولية إدارية حقيقية زمن "التأجيل" أو "المعالجة لاحقًا" انتهى ببساطة: risk management بقت في قلب المشهد… مش وظيفة مساندة. ٣- فرصة حقيقية لأصحاب المشروعات — لكن للي جاهز فقط اللي عنده مشروع صغير أو متوسط، أو بيفكر يبدأ، لازم يفهم إن الفترة الجاية هتشهد: - برامج تمويل أكتر - تسهيلات أكبر - منافسة بين البنوك على جذب عملاء الـ smes بس التمويل مش هيروح لأي حد… هيروح للي مؤهل. ٤- الجاهزية بقت كلمة السر المشروع اللي عنده: قوائم مالية واضحة تدفقات نقدية مفهومة نموذج عمل واقعي حوكمة وإدارة مالية منضبطة هو اللي هيستفيد من الموجة الجاية. لأن البنوك نفسها بقت تحت ضغط رقابي… فمش هتغامر بتمويل مشروعات غير مؤهلة. رأيي الشخصي: إحنا داخلين على مرحلة "نضج رقابي" حقيقية اللي بيحصل حاليًا مش مجرد تطبيق تعليمات بل ده إعادة تشكيل لسلوك السوق المصرفي بالكامل. - ضغط على البنوك - ضغط على إدارات المخاطر - ضغط على جودة المحافظ الائتمانية - و فرص أكبر لقطاع الـ smes وده في رأيي من أهم التحولات اللي هتأثر على الاقتصاد الحقيقي في مصر خلال السنين الجاية. #esg #sustainability #البنك_المركزي #إدارة_المخاطر #smes #الاقتصاد_المصري #risk_management #تمويل #حوكمة #القطاع_المصرفي «المركزي» يعزز الرقابة المشددة.. ويفرض غرامات على عدة بنوك | المصري اليوم</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="R42" t="n">
-        <v>41</v>
-      </c>
-      <c r="S42" t="inlineStr">
+      <c r="R44" t="n">
+        <v>43</v>
+      </c>
+      <c r="S44" t="inlineStr">
         <is>
           <t>#esg #sustainability #البنك_المركزي #إدارة_المخاطر #smes #الاقتصاد_المصري #risk_management #تمويل #حوكمة #القطاع_المصرفي «المركزي» يعزز الرقابة المشددة.. • - 1.115 مليار على المصرف المتحد the united# bank. • - 778 مليون جنيه غرامة على بنك أبوظبي التجاري adcb#.</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>4. Abu Dhabi Commercial Bank (ADCB)</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>Abu Dhabi Commercial Bank (ADCB)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
+    <row r="45">
+      <c r="A45" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Afra Al Otaiba</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
+      <c r="C45" s="2" t="n">
         <v>46138.42488792824</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Proud to have completed our Industry Research Project on Abu Dhabi Islamic Bank (ADIB), where we explored the role of Islamic banking in the UAE and how institutions like ADIB combine ethical values with modern financial innovation.
 This experience gave us the opportunity to connect what we learn in class with real-world insights, especially through our discussion with industry professionals. It deepened our understanding of how trust, transparency, and customer relationships shape the banking sector today.
@@ -5406,108 +5630,108 @@
 Special thanks to our professor Ms. Alaa Q. Al Ameri  for the guidance and support throughout this project.</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E45" t="n">
         <v>4</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/afra-al-otaiba-5302b53a9_proud-to-have-completed-our-industry-research-activity-7454049583778684928--0kn?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACAuXJMB_Tg4ICdAktyCfDr2_F5ay5Kzuqw</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/afra-al-otaiba-5302b53a9_proud-to-have-completed-our-industry-research-activity-7454049583778684928--0kn?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACkYlAQBRTNz8CdXZeg6hzVz7QVXcc1syiY</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>urn:li:activity:7454049583778684928</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>ADIB</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>proud to have completed our industry research project on abu dhabi islamic bank (adib), where we explored the role of islamic banking in the uae and how institutions like adib combine ethical values with modern financial innovation. this experience gave us the opportunity to connect what we learn in class with real-world insights, especially through our discussion with industry professionals. it deepened our understanding of how trust, transparency, and customer relationships shape the banking sector today. as part of the project, we designed a full interactive kiosk along with supporting visuals and an engaging activity, aiming to present adib in a way that reflects both professionalism and innovation. grateful and proud of what we created together. looking forward to building on this experience and continuing to explore the intersection of ethics, finance, and innovation. special thanks to our professor ms. alaa q. al ameri for the guidance and support throughout this project.</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Afra Al Otaiba</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>proud to have completed our industry research project on abu dhabi islamic bank (adib), where we explored the role of islamic banking in the uae and how institutions like adib combine ethical values with modern financial innovation. this experience gave us the opportunity to connect what we learn in class with real-world insights, especially through our discussion with industry professionals. it deepened our understanding of how trust, transparency, and customer relationships shape the banking sector today. as part of the project, we designed a full interactive kiosk along with supporting visuals and an engaging activity, aiming to present adib in a way that reflects both professionalism and innovation. grateful and proud of what we created together. looking forward to building on this experience and continuing to explore the intersection of ethics, finance, and innovation. special thanks to our professor ms. alaa q. al ameri for the guidance and support throughout this project.</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R43" t="n">
-        <v>42</v>
-      </c>
-      <c r="S43" t="inlineStr">
+      <c r="R45" t="n">
+        <v>44</v>
+      </c>
+      <c r="S45" t="inlineStr">
         <is>
           <t>as part of the project, we designed a full interactive kiosk along with supporting visuals and an engaging activity, aiming to present adib in a way that reflects both professionalism and innovation. • this experience gave us the opportunity to connect what we learn in class with real-world insights, especially through our discussion with industry professionals. • it deepened our understanding of how trust, transparency, and customer relationships shape the banking sector today.</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
+    <row r="46">
+      <c r="A46" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Nitin Goel</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
+      <c r="C46" s="2" t="n">
         <v>46138.33334766204</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>I've been sitting with the CBUAE AlTareq documentation for a few months now. Reading the regulation, mapping the consent flows, tracing how Nebras actually routes API calls between a bank, a customer, and their accounts at three other banks.
 At some point I stopped reading and started building.
@@ -5525,108 +5749,108 @@
 #OpenFinance #AlTareq #CBUAE #AISP #Nebras #UAE #FinTech #OpenBanking #DigitalBanking #ProductManagement #UAEFinTech #FAPI2.0 #Dubai #AbuDhabi</t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="E46" t="n">
         <v>3</v>
       </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="inlineStr">
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>document</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/nitingoel3001_nitin-altareq-aisp-implementation-full-deck-activity-7454016410697048065-o2YT?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACAuXJMB_Tg4ICdAktyCfDr2_F5ay5Kzuqw</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/nitingoel3001_nitin-altareq-aisp-implementation-full-deck-activity-7454016410697048065-o2YT?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACkYlAQBRTNz8CdXZeg6hzVz7QVXcc1syiY</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>urn:li:activity:7454016410697048065</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>ADIB</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>i've been sitting with the cbuae altareq documentation for a few months now. reading the regulation, mapping the consent flows, tracing how nebras actually routes api calls between a bank, a customer, and their accounts at three other banks. at some point i stopped reading and started building. the result is a full aisp implementation deck - not a regulation summary, not a slide full of bullet points about 'digital transformation'. an actual product architecture presentation: - system architecture with all 5 ecosystem participants - swimlane process flow - customer, bank app, nebras, lfi - across 8 steps - data flow diagram showing exactly how data moves from lfi to dashboard - consent lifecycle state machine (initiation → active → expiring → expired/revoked) - fapi 2.0 security stack, layered - all 6 nebras api endpoints mapped with data, frequency, and compliance obligation adib - abu dhabi islamic bank already holds the first tpp licence. phase 1 is not a roadmap item - it's a sprint. if you're building open finance at a uae bank, lfi, or fintech, or if you're trying to explain the altareq architecture to a room of engineers and compliance officers who've never seen it laid out clearly this deck is for you. dropping the full deck below. no form, no email wall. and if something in the flow looks wrong to you, tell me. i'd rather fix it than present it. #openfinance #altareq #cbuae #aisp #nebras #uae #fintech #openbanking #digitalbanking #productmanagement #uaefintech #fapi2.0 #dubai #abudhabi</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Nitin Goel</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>i've been sitting with the cbuae altareq documentation for a few months now. reading the regulation, mapping the consent flows, tracing how nebras actually routes api calls between a bank, a customer, and their accounts at three other banks. at some point i stopped reading and started building. the result is a full aisp implementation deck - not a regulation summary, not a slide full of bullet points about 'digital transformation'. an actual product architecture presentation: - system architecture with all 5 ecosystem participants - swimlane process flow - customer, bank app, nebras, lfi - across 8 steps - data flow diagram showing exactly how data moves from lfi to dashboard - consent lifecycle state machine (initiation → active → expiring → expired/revoked) - fapi 2.0 security stack, layered - all 6 nebras api endpoints mapped with data, frequency, and compliance obligation adib - abu dhabi islamic bank already holds the first tpp licence. phase 1 is not a roadmap item - it's a sprint. if you're building open finance at a uae bank, lfi, or fintech, or if you're trying to explain the altareq architecture to a room of engineers and compliance officers who've never seen it laid out clearly this deck is for you. dropping the full deck below. no form, no email wall. and if something in the flow looks wrong to you, tell me. i'd rather fix it than present it. #openfinance #altareq #cbuae #aisp #nebras #uae #fintech #openbanking #digitalbanking #productmanagement #uaefintech #fapi2.0 #dubai #abudhabi</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R44" t="n">
-        <v>43</v>
-      </c>
-      <c r="S44" t="inlineStr">
+      <c r="R46" t="n">
+        <v>45</v>
+      </c>
+      <c r="S46" t="inlineStr">
         <is>
           <t>reading the regulation, mapping the consent flows, tracing how nebras actually routes api calls between a bank, a customer, and their accounts at three other banks. • #openfinance #altareq #cbuae #aisp #nebras #uae #fintech #openbanking #digitalbanking #productmanagement #uaefintech #fapi2.0 #dubai #abudhabi • the result is a full aisp implementation deck - not a regulation summary, not a slide full of bullet points about 'digital transformation'.</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
+    <row r="47">
+      <c r="A47" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Muhammed ahmed</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
+      <c r="C47" s="2" t="n">
         <v>46138.98273563657</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>I'm excited to share that I’ve been accepted at Abu Dhabi Islamic Bank - Egypt (ADIB) as a Credit Maintenance Apprentice within the Consumer Operations department.
 Grateful for this opportunity and looking forward to learning, growing, and contributing to my team.
@@ -5635,108 +5859,108 @@
 #ConsumerOperations</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="E47" t="n">
         <v>1</v>
       </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/muhammed-ahmed-5b424b242_bank-banking-consumeroperations-activity-7454251741019107328-2kVi?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFmepswBpvzzEmBcMoTeKybuJA-Yp5AO8js</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/muhammed-ahmed-5b424b242_bank-banking-consumeroperations-activity-7454251741019107328-2kVi?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAABxDsfABgJsLEUdI8vdnLv9UfDiShk5adv4</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>urn:li:activity:7454251741019107328</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>ADIB</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>i'm excited to share that i’ve been accepted at abu dhabi islamic bank - egypt (adib) as a credit maintenance apprentice within the consumer operations department. grateful for this opportunity and looking forward to learning, growing, and contributing to my team. #bank #banking #consumeroperations</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Muhammed ahmed</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>i'm excited to share that i’ve been accepted at abu dhabi islamic bank - egypt (adib) as a credit maintenance apprentice within the consumer operations department. grateful for this opportunity and looking forward to learning, growing, and contributing to my team. #bank #banking #consumeroperations</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R45" t="n">
-        <v>44</v>
-      </c>
-      <c r="S45" t="inlineStr">
+      <c r="R47" t="n">
+        <v>46</v>
+      </c>
+      <c r="S47" t="inlineStr">
         <is>
           <t>i'm excited to share that i’ve been accepted at abu dhabi islamic bank - egypt (adib) as a credit maintenance apprentice within the consumer operations department. • grateful for this opportunity and looking forward to learning, growing, and contributing to my team. • #bank #banking #consumeroperations</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
+    <row r="48">
+      <c r="A48" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Naglaa Moawad</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C48" s="2" t="n">
         <v>46138.92520032408</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>انا زوجي مدير حسابات بيدور ع شغل بقاله فترة كبيرة جدا بعد ما ساب شغله الأخير لكن مفيش اي رد واتحطينا ف ظروف صعبة واخيرا اتقبل الحمدلله بعد ما جاله كذا انتر ڤيو وكل دا بفضل ربنا ثم دكتور أحمد عبدالقادر مدير الموارد البشرية الغني عن التعريف طبعا بعد ما عمله سي ڤي قوي ATS وبروفايل لينكدن احترافي واجتاز نظام الفلترة الاولى لكل البنوك والشركات اللي قدم عليها وجاله مقابلات كتير جدا بعد ما فقدنا الامل ودا من الناس القليلة اللي قابلتنا بتراعي ربنا ف شغلها والله وانا ضغط عليه عشان انزل الفيد باك دا انا عارفه انه مش محتاج حاجة بس دي اقل حاجة ممكن اقدمهاله وبالمرة ممكن يكون فك كرب عن اي حد بيمر بنفس الظروف دي وهو عامل عرض كويس لو هتعمل بكدچ السي ڤي ولينكدن والكڤر لتر مع بعضهم ودا رابط الواتس بتاعه والرقم
 👉📞https://lnkd.in/e9_RyfHy
@@ -5744,215 +5968,215 @@
 Majid Al Futtaim Al-Futtaim Mashreq ADIB - Abu Dhabi Islamic Bank CIB Egypt e&amp; Egypt National Bank of Egypt (NBE)</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>27</v>
-      </c>
-      <c r="F46" t="n">
+      <c r="E48" t="n">
+        <v>29</v>
+      </c>
+      <c r="F48" t="n">
         <v>13</v>
       </c>
-      <c r="G46" t="n">
-        <v>3</v>
-      </c>
-      <c r="H46" t="inlineStr">
+      <c r="G48" t="n">
+        <v>4</v>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/naglaa-moawad-288141406_%D8%A7%D9%86%D8%A7-%D8%B2%D9%88%D8%AC%D9%8A-%D9%85%D8%AF%D9%8A%D8%B1-%D8%AD%D8%B3%D8%A7%D8%A8%D8%A7%D8%AA-%D8%A8%D9%8A%D8%AF%D9%88%D8%B1-%D8%B9-%D8%B4%D8%BA%D9%84-%D8%A8%D9%82%D8%A7%D9%84%D9%87-%D9%81%D8%AA%D8%B1%D8%A9-activity-7454230890919911424--fdR?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFmepswBpvzzEmBcMoTeKybuJA-Yp5AO8js</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/naglaa-moawad-288141406_%D8%A7%D9%86%D8%A7-%D8%B2%D9%88%D8%AC%D9%8A-%D9%85%D8%AF%D9%8A%D8%B1-%D8%AD%D8%B3%D8%A7%D8%A8%D8%A7%D8%AA-%D8%A8%D9%8A%D8%AF%D9%88%D8%B1-%D8%B9-%D8%B4%D8%BA%D9%84-%D8%A8%D9%82%D8%A7%D9%84%D9%87-%D9%81%D8%AA%D8%B1%D8%A9-activity-7454230890919911424--fdR?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAABxDsfABgJsLEUdI8vdnLv9UfDiShk5adv4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>urn:li:activity:7454230890919911424</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>ADIB</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>انا زوجي مدير حسابات بيدور ع شغل بقاله فترة كبيرة جدا بعد ما ساب شغله الأخير لكن مفيش اي رد واتحطينا ف ظروف صعبة واخيرا اتقبل الحمدلله بعد ما جاله كذا انتر ڤيو وكل دا بفضل ربنا ثم دكتور أحمد عبدالقادر مدير الموارد البشرية الغني عن التعريف طبعا بعد ما عمله سي ڤي قوي ats وبروفايل لينكدن احترافي واجتاز نظام الفلترة الاولى لكل البنوك والشركات اللي قدم عليها وجاله مقابلات كتير جدا بعد ما فقدنا الامل ودا من الناس القليلة اللي قابلتنا بتراعي ربنا ف شغلها والله وانا ضغط عليه عشان انزل الفيد باك دا انا عارفه انه مش محتاج حاجة بس دي اقل حاجة ممكن اقدمهاله وبالمرة ممكن يكون فك كرب عن اي حد بيمر بنفس الظروف دي وهو عامل عرض كويس لو هتعمل بكدچ السي ڤي ولينكدن والكڤر لتر مع بعضهم ودا رابط الواتس بتاعه والرقم  او الرقم 01016125301(2+) majid al futtaim al-futtaim mashreq adib - abu dhabi islamic bank cib egypt e&amp; egypt national bank of egypt (nbe)</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Naglaa Moawad</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>انا زوجي مدير حسابات بيدور ع شغل بقاله فترة كبيرة جدا بعد ما ساب شغله الأخير لكن مفيش اي رد واتحطينا ف ظروف صعبة واخيرا اتقبل الحمدلله بعد ما جاله كذا انتر ڤيو وكل دا بفضل ربنا ثم دكتور أحمد عبدالقادر مدير الموارد البشرية الغني عن التعريف طبعا بعد ما عمله سي ڤي قوي ats وبروفايل لينكدن احترافي واجتاز نظام الفلترة الاولى لكل البنوك والشركات اللي قدم عليها وجاله مقابلات كتير جدا بعد ما فقدنا الامل ودا من الناس القليلة اللي قابلتنا بتراعي ربنا ف شغلها والله وانا ضغط عليه عشان انزل الفيد باك دا انا عارفه انه مش محتاج حاجة بس دي اقل حاجة ممكن اقدمهاله وبالمرة ممكن يكون فك كرب عن اي حد بيمر بنفس الظروف دي وهو عامل عرض كويس لو هتعمل بكدچ السي ڤي ولينكدن والكڤر لتر مع بعضهم ودا رابط الواتس بتاعه والرقم  او الرقم 01016125301(2+) majid al futtaim al-futtaim mashreq adib - abu dhabi islamic bank cib egypt e&amp; egypt national bank of egypt (nbe)</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R46" t="n">
-        <v>45</v>
-      </c>
-      <c r="S46" t="inlineStr">
+      <c r="R48" t="n">
+        <v>47</v>
+      </c>
+      <c r="S48" t="inlineStr">
         <is>
           <t>انا زوجي مدير حسابات بيدور ع شغل بقاله فترة كبيرة جدا بعد ما ساب شغله الأخير لكن مفيش اي رد واتحطينا ف ظروف صعبة واخيرا …</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
+    <row r="49">
+      <c r="A49" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Adel Ashraf Samir</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C49" s="2" t="n">
         <v>46138.90918895834</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>I would like to express my pleasure to ADIB for his continuous support in providing a valuable course like that.
 Abu Dhabi Islamic Bank - Egypt 💪😍</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="E49" t="n">
         <v>6</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F49" t="n">
         <v>1</v>
       </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="inlineStr">
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/adel-ashraf-samir-27b731215_i-would-like-to-express-my-pleasure-to-adib-activity-7454225088595546112-L-Mz?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFmepswBpvzzEmBcMoTeKybuJA-Yp5AO8js</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/adel-ashraf-samir-27b731215_i-would-like-to-express-my-pleasure-to-adib-activity-7454225088595546112-L-Mz?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAABxDsfABgJsLEUdI8vdnLv9UfDiShk5adv4</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>urn:li:activity:7454225088595546112</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>ADIB</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>i would like to express my pleasure to adib for his continuous support in providing a valuable course like that. abu dhabi islamic bank - egypt</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>Adel Ashraf Samir</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>i would like to express my pleasure to adib for his continuous support in providing a valuable course like that. abu dhabi islamic bank - egypt</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R47" t="n">
-        <v>46</v>
-      </c>
-      <c r="S47" t="inlineStr">
+      <c r="R49" t="n">
+        <v>48</v>
+      </c>
+      <c r="S49" t="inlineStr">
         <is>
           <t>i would like to express my pleasure to adib for his continuous support in providing a valuable course like that. • abu dhabi islamic bank - egypt</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
+    <row r="50">
+      <c r="A50" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Habiba Tarek</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
+      <c r="C50" s="2" t="n">
         <v>46138.87866207176</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Celebrating the achievements, leadership, and ongoing contributions of women across Abu Dhabi Islamic Bank - Egypt, and the impact they continue to create in our workplace
 Proud to be part of a workplace that believes in empowerment, inclusion, and lifting each other higher.
@@ -5960,108 +6184,108 @@
 #WomensDay #ADIB #EmpowerWomen #Inclusion #WorkplaceCulture</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v>64</v>
-      </c>
-      <c r="F48" t="n">
+      <c r="E50" t="n">
+        <v>65</v>
+      </c>
+      <c r="F50" t="n">
         <v>1</v>
       </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="inlineStr">
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/habiba-tarek-97621921a_womensday-adib-empowerwomen-activity-7454214026021986304-wRB5?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFmepswBpvzzEmBcMoTeKybuJA-Yp5AO8js</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/habiba-tarek-97621921a_womensday-adib-empowerwomen-activity-7454214026021986304-wRB5?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAABxDsfABgJsLEUdI8vdnLv9UfDiShk5adv4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>urn:li:activity:7454214026021986304</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>ADIB</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>celebrating the achievements, leadership, and ongoing contributions of women across abu dhabi islamic bank - egypt, and the impact they continue to create in our workplace proud to be part of a workplace that believes in empowerment, inclusion, and lifting each other higher. here’s to more growth, breaking barriers, and supporting one another to achieve even greater success. #womensday #adib #empowerwomen #inclusion #workplaceculture</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>Habiba Tarek</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>celebrating the achievements, leadership, and ongoing contributions of women across abu dhabi islamic bank - egypt, and the impact they continue to create in our workplace proud to be part of a workplace that believes in empowerment, inclusion, and lifting each other higher. here’s to more growth, breaking barriers, and supporting one another to achieve even greater success. #womensday #adib #empowerwomen #inclusion #workplaceculture</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R48" t="n">
-        <v>47</v>
-      </c>
-      <c r="S48" t="inlineStr">
+      <c r="R50" t="n">
+        <v>49</v>
+      </c>
+      <c r="S50" t="inlineStr">
         <is>
           <t>here’s to more growth, breaking barriers, and supporting one another to achieve even greater success. • #womensday #adib #empowerwomen #inclusion #workplaceculture</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
+    <row r="51">
+      <c r="A51" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Amany Elhariry , SHRM</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C51" s="2" t="n">
         <v>46138.85020887732</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Why "just a gift" wasn't enough this year ♥️
 At Abu Dhabi Islamic Bank - Egypt  , we wanted to ensure the women who drive our bank's success truly feel the appreciation they deserve.
@@ -6071,108 +6295,108 @@
 #ADIB #IWD #WomenInBanking #WorkHardCelebrateHarder</t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v>129</v>
-      </c>
-      <c r="F49" t="n">
+      <c r="E51" t="n">
+        <v>138</v>
+      </c>
+      <c r="F51" t="n">
         <v>5</v>
       </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="inlineStr">
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/amany-elhariry-shrm-a34255150_adib-iwd-womeninbanking-activity-7454203714929573888-VAr7?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFmepswBpvzzEmBcMoTeKybuJA-Yp5AO8js</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/amany-elhariry-shrm-a34255150_adib-iwd-womeninbanking-activity-7454203714929573888-VAr7?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAABxDsfABgJsLEUdI8vdnLv9UfDiShk5adv4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>urn:li:activity:7454203714929573888</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>ADIB</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>why "just a gift" wasn't enough this year at abu dhabi islamic bank - egypt , we wanted to ensure the women who drive our bank's success truly feel the appreciation they deserve. i’m so happy my idea for a sensory gift was implemented. we curated an experience that touches every sense—from scent to touch—to pamper the talented women who contribute so much to our growth every day. being a professional doesn't mean we can’t be pampered. to the incredible women of adib: you work hard. now, let’s celebrate even harder! #adib #iwd #womeninbanking #workhardcelebrateharder</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>Amany Elhariry , SHRM</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>why "just a gift" wasn't enough this year at abu dhabi islamic bank - egypt , we wanted to ensure the women who drive our bank's success truly feel the appreciation they deserve. i’m so happy my idea for a sensory gift was implemented. we curated an experience that touches every sense—from scent to touch—to pamper the talented women who contribute so much to our growth every day. being a professional doesn't mean we can’t be pampered. to the incredible women of adib: you work hard. now, let’s celebrate even harder! #adib #iwd #womeninbanking #workhardcelebrateharder</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R49" t="n">
-        <v>48</v>
-      </c>
-      <c r="S49" t="inlineStr">
+      <c r="R51" t="n">
+        <v>50</v>
+      </c>
+      <c r="S51" t="inlineStr">
         <is>
           <t>why "just a gift" wasn't enough this year at abu dhabi islamic bank - egypt , we wanted to ensure the women who drive our bank's success truly feel the appreciation they deserve. • we curated an experience that touches every sense—from scent to touch—to pamper the talented women who contribute so much to our growth every day. • to the incredible women of adib: you work hard.</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
+    <row r="52">
+      <c r="A52" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Merna Taha</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
+      <c r="C52" s="2" t="n">
         <v>46138.75501918981</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>This year, Abu Dhabi Islamic Bank - Egypt  celebrated Women in an unforgettable way. 
 Instead of a traditional gift, we received a “5 senses” experience. Each element was thoughtfully chosen to engage sight, smell, taste, touch, and sound… a reminder to pause, feel, and reconnect with ourselves beyond the rush of daily responsibilities.
@@ -6180,108 +6404,108 @@
 The biggest thank you to the brightest woman behind this idea Amany Elhariry , SHRM 🤩</t>
         </is>
       </c>
-      <c r="E50" t="n">
-        <v>26</v>
-      </c>
-      <c r="F50" t="n">
+      <c r="E52" t="n">
+        <v>27</v>
+      </c>
+      <c r="F52" t="n">
         <v>2</v>
       </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="inlineStr">
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/merna-taha_this-year-abu-dhabi-islamic-bank-egypt-activity-7454169219342151680-sbz5?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFmepswBpvzzEmBcMoTeKybuJA-Yp5AO8js</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/merna-taha_this-year-abu-dhabi-islamic-bank-egypt-activity-7454169219342151680-sbz5?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAABxDsfABgJsLEUdI8vdnLv9UfDiShk5adv4</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>urn:li:activity:7454169219342151680</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>ADIB</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>this year, abu dhabi islamic bank - egypt celebrated women in an unforgettable way. instead of a traditional gift, we received a “5 senses” experience. each element was thoughtfully chosen to engage sight, smell, taste, touch, and sound… a reminder to pause, feel, and reconnect with ourselves beyond the rush of daily responsibilities. super grateful for such an amazing gesture! the biggest thank you to the brightest woman behind this idea amany elhariry , shrm</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>Merna Taha</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>this year, abu dhabi islamic bank - egypt celebrated women in an unforgettable way. instead of a traditional gift, we received a “5 senses” experience. each element was thoughtfully chosen to engage sight, smell, taste, touch, and sound… a reminder to pause, feel, and reconnect with ourselves beyond the rush of daily responsibilities. super grateful for such an amazing gesture! the biggest thank you to the brightest woman behind this idea amany elhariry , shrm</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R50" t="n">
-        <v>49</v>
-      </c>
-      <c r="S50" t="inlineStr">
+      <c r="R52" t="n">
+        <v>51</v>
+      </c>
+      <c r="S52" t="inlineStr">
         <is>
           <t>each element was thoughtfully chosen to engage sight, smell, taste, touch, and sound… a reminder to pause, feel, and reconnect with ourselves beyond the rush of daily responsibilities. • this year, abu dhabi islamic bank - egypt celebrated women in an unforgettable way. • the biggest thank you to the brightest woman behind this idea amany elhariry , shrm</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
+    <row r="53">
+      <c r="A53" s="1" t="n">
         <v>67</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Talent Bridge</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
+      <c r="C53" s="2" t="n">
         <v>46138.75000534722</v>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Duane Maxwell is a senior compliance and governance leader specializing in regulatory compliance, financial crime risk, compliance assurance, and enterprise governance transformation across global banking institutions.
 He currently serves as Chief Compliance Officer at ADIB - Abu Dhabi Islamic Bank, where he leads enterprise-wide compliance strategy, strengthens regulatory governance frameworks, and drives a culture of compliance excellence across the organization.
@@ -6292,112 +6516,112 @@
 #Compliance #RegulatoryRisk #Governance #FinancialCrime #RiskManagement #Banking #TalentBridge #TBRecognized</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="E53" t="n">
         <v>3</v>
       </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="inlineStr">
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/talentbridge0_compliance-regulatoryrisk-governance-activity-7454167402386427904-xhkX?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFmepswBpvzzEmBcMoTeKybuJA-Yp5AO8js</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/talentbridge0_compliance-regulatoryrisk-governance-activity-7454167402386427904-xhkX?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAABxDsfABgJsLEUdI8vdnLv9UfDiShk5adv4</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>urn:li:activity:7454167402386427904</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>ADIB</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>duane maxwell is a senior compliance and governance leader specializing in regulatory compliance, financial crime risk, compliance assurance, and enterprise governance transformation across global banking institutions. he currently serves as chief compliance officer at adib - abu dhabi islamic bank, where he leads enterprise-wide compliance strategy, strengthens regulatory governance frameworks, and drives a culture of compliance excellence across the organization. previously, he held roles including acting group head of compliance at adib - abu dhabi islamic bank, head of corporate governance at banking, head, compliance governance &amp; assurance at abu dhabi -based bank, head, compliance assurance at uae based bank, director compliance (seconded to morgan stanley) at fti consulting, senior manager, financial crime and &amp; regulatory compliance assurance at hsbc, vice president - compliance assurance at barclays uk, associate director, compliance barclays internal audit at barclays, regional compliance officer, uk &amp; ireland at aig, senior compliance monitoring manager at aig europe (uk) limited, head of compliance at aig - unat direct insurance limited, audit and compliance manager at aig europe (uk) limited, and assistant manager, compliance &amp; sales risk at lloyds private banking, where he contributed to global compliance assurance frameworks, regulatory risk assessment, financial crime compliance oversight, conduct risk management, internal audit advisory, governance structure development, and enterprise-wide compliance monitoring across leading financial institutions in the uk, europe, and the uae. earlier, he was assistant manager, compliance &amp; sales risk at lloyds private banking, building a strong foundation in compliance risk, sales governance, and regulatory assurance within retail banking operations. he completed his education including bsc. (hons) management studies at unversity of the west indies, diploma in compliance at @international compliance association, mba at university of lincoln, cxcs and gce ao levels at st mary's college, st lucia, a levels at sir arthur lewis community college - st lucia, and cxcs and gce ao levels at the university of law. with over 20+ years of experience, duane maxwell is recognized for expertise in global compliance leadership, regulatory governance, financial crime risk management, and building strong compliance cultures across multinational banking and financial services organizations. #compliance #regulatoryrisk #governance #financialcrime #riskmanagement #banking #talentbridge #tbrecognized</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>Talent Bridge</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>duane maxwell is a senior compliance and governance leader specializing in regulatory compliance, financial crime risk, compliance assurance, and enterprise governance transformation across global banking institutions. he currently serves as chief compliance officer at adib - abu dhabi islamic bank, where he leads enterprise-wide compliance strategy, strengthens regulatory governance frameworks, and drives a culture of compliance excellence across the organization. previously, he held roles including acting group head of compliance at adib - abu dhabi islamic bank, head of corporate governance at banking, head, compliance governance &amp; assurance at abu dhabi -based bank, head, compliance assurance at uae based bank, director compliance (seconded to morgan stanley) at fti consulting, senior manager, financial crime and &amp; regulatory compliance assurance at hsbc, vice president - compliance assurance at barclays uk, associate director, compliance barclays internal audit at barclays, regional compliance officer, uk &amp; ireland at aig, senior compliance monitoring manager at aig europe (uk) limited, head of compliance at aig - unat direct insurance limited, audit and compliance manager at aig europe (uk) limited, and assistant manager, compliance &amp; sales risk at lloyds private banking, where he contributed to global compliance assurance frameworks, regulatory risk assessment, financial crime compliance oversight, conduct risk management, internal audit advisory, governance structure development, and enterprise-wide compliance monitoring across leading financial institutions in the uk, europe, and the uae. earlier, he was assistant manager, compliance &amp; sales risk at lloyds private banking, building a strong foundation in compliance risk, sales governance, and regulatory assurance within retail banking operations. he completed his education including bsc. (hons) management studies at unversity of the west indies, diploma in compliance at @international compliance association, mba at university of lincoln, cxcs and gce ao levels at st mary's college, st lucia, a levels at sir arthur lewis community college - st lucia, and cxcs and gce ao levels at the university of law. with over 20+ years of experience, duane maxwell is recognized for expertise in global compliance leadership, regulatory governance, financial crime risk management, and building strong compliance cultures across multinational banking and financial services organizations. #compliance #regulatoryrisk #governance #financialcrime #riskmanagement #banking #talentbridge #tbrecognized</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R51" t="n">
-        <v>50</v>
-      </c>
-      <c r="S51" t="inlineStr">
+      <c r="R53" t="n">
+        <v>52</v>
+      </c>
+      <c r="S53" t="inlineStr">
         <is>
           <t>#compliance #regulatoryrisk #governance #financialcrime #riskmanagement #banking #talentbridge #tbrecognized • he completed his education including bsc.</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
+    <row r="54">
+      <c r="A54" s="1" t="n">
         <v>68</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Tarek Rashwan</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
+      <c r="C54" s="2" t="n">
         <v>46138.73126046296</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>مساء الخير انا طارق رشوان خريج كلية الاعمال بتقدير أمتياز A (حديث التخرج) دفعة ٢٠٢٤ خلصت جيشي وكونت بسعي ع وظيفة في أحد البنك اللي افدها وتفدني وأثبت فيها..
 National Bank of Egypt (NBE) 
@@ -6418,108 +6642,108 @@
 Suez Canal Bank</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="E54" t="n">
         <v>18</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F54" t="n">
         <v>2</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G54" t="n">
         <v>1</v>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/tarek-rashwan-02978b3b3_%D9%85%D8%B3%D8%A7%D8%A1-%D8%A7%D9%84%D8%AE%D9%8A%D8%B1-%D8%A7%D9%86%D8%A7-%D8%B7%D8%A7%D8%B1%D9%82-%D8%B1%D8%B4%D9%88%D8%A7%D9%86-%D8%AE%D8%B1%D9%8A%D8%AC-%D9%83%D9%84%D9%8A%D8%A9-%D8%A7%D9%84%D8%A7%D8%B9%D9%85%D8%A7%D9%84-activity-7454160609467691008-NwD0?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFmepswBpvzzEmBcMoTeKybuJA-Yp5AO8js</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/tarek-rashwan-02978b3b3_%D9%85%D8%B3%D8%A7%D8%A1-%D8%A7%D9%84%D8%AE%D9%8A%D8%B1-%D8%A7%D9%86%D8%A7-%D8%B7%D8%A7%D8%B1%D9%82-%D8%B1%D8%B4%D9%88%D8%A7%D9%86-%D8%AE%D8%B1%D9%8A%D8%AC-%D9%83%D9%84%D9%8A%D8%A9-%D8%A7%D9%84%D8%A7%D8%B9%D9%85%D8%A7%D9%84-activity-7454160609467691008-NwD0?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAABxDsfABgJsLEUdI8vdnLv9UfDiShk5adv4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>urn:li:activity:7454160609467691008</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>ADIB</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>مساء الخير انا طارق رشوان خريج كلية الاعمال بتقدير أمتياز a (حديث التخرج) دفعة ٢٠٢٤ خلصت جيشي وكونت بسعي ع وظيفة في أحد البنك اللي افدها وتفدني وأثبت فيها.. national bank of egypt (nbe) banque misr banque du caire national bank of kuwait agricultural bank of egypt arab african international bank abu dhabi islamic bank - egypt bank abc islamic cib egypt qnb egypt بنك التعمير والإسكان hd bank egbank adib - abu dhabi islamic bank faisal islamic bank of egypt alexbank suez canal bank</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>Tarek Rashwan</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>مساء الخير انا طارق رشوان خريج كلية الاعمال بتقدير أمتياز a (حديث التخرج) دفعة ٢٠٢٤ خلصت جيشي وكونت بسعي ع وظيفة في أحد البنك اللي افدها وتفدني وأثبت فيها.. national bank of egypt (nbe) banque misr banque du caire national bank of kuwait agricultural bank of egypt arab african international bank abu dhabi islamic bank - egypt bank abc islamic cib egypt qnb egypt بنك التعمير والإسكان hd bank egbank adib - abu dhabi islamic bank faisal islamic bank of egypt alexbank suez canal bank</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R52" t="n">
-        <v>51</v>
-      </c>
-      <c r="S52" t="inlineStr">
+      <c r="R54" t="n">
+        <v>53</v>
+      </c>
+      <c r="S54" t="inlineStr">
         <is>
           <t>مساء الخير انا طارق رشوان خريج كلية الاعمال بتقدير أمتياز a (حديث التخرج) دفعة ٢٠٢٤ خلصت جيشي وكونت بسعي ع وظيفة في أحد البنك اللي افدها وتفدني وأثبت فيها..</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
+    <row r="55">
+      <c r="A55" s="1" t="n">
         <v>69</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Omnya Hanafy</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
+      <c r="C55" s="2" t="n">
         <v>46138.69169869213</v>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Grateful for the little moments that add a beautiful touch to my day ✨
 A gentle reminder I see every day: 
@@ -6529,108 +6753,108 @@
 #ADIB</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="E55" t="n">
         <v>50</v>
       </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="inlineStr">
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/omnya-hanafy-479009198_adib-activity-7454146272762052608-34xc?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFmepswBpvzzEmBcMoTeKybuJA-Yp5AO8js</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/omnya-hanafy-479009198_adib-activity-7454146272762052608-34xc?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAABxDsfABgJsLEUdI8vdnLv9UfDiShk5adv4</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>urn:li:activity:7454146272762052608</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>ADIB</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>grateful for the little moments that add a beautiful touch to my day a gentle reminder i see every day: "don’t forget how amazing you are" thank you for the thoughtful gesture and for consistently creating a positive and inspiring work environment. proud to be part of a team that believes in appreciation, growth, and continuous support abu dhabi islamic bank - egypt #adib</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>Omnya Hanafy</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>grateful for the little moments that add a beautiful touch to my day a gentle reminder i see every day: "don’t forget how amazing you are" thank you for the thoughtful gesture and for consistently creating a positive and inspiring work environment. proud to be part of a team that believes in appreciation, growth, and continuous support abu dhabi islamic bank - egypt #adib</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R53" t="n">
-        <v>52</v>
-      </c>
-      <c r="S53" t="inlineStr">
+      <c r="R55" t="n">
+        <v>54</v>
+      </c>
+      <c r="S55" t="inlineStr">
         <is>
           <t>proud to be part of a team that believes in appreciation, growth, and continuous support abu dhabi islamic bank - egypt #adib</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
+    <row r="56">
+      <c r="A56" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Abdullah Mohamed</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
+      <c r="C56" s="2" t="n">
         <v>46138.68332947916</v>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>CIB Egypt
 Bank ABC 
@@ -6642,108 +6866,108 @@
 Crédit Agricole next bank (Suisse) SA</t>
         </is>
       </c>
-      <c r="E54" t="n">
+      <c r="E56" t="n">
         <v>7</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F56" t="n">
         <v>1</v>
       </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="inlineStr">
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/abdullah-mohamed-86b5321b8_cib-egypt-bank-abc-hsbc-corporate-and-institutional-activity-7454143239860871168-RzR1?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAE4ybtUBRdwFJ0EDIJFhItHwBDR1cpnZEO0</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/abdullah-mohamed-86b5321b8_cib-egypt-bank-abc-hsbc-corporate-and-institutional-activity-7454143239860871168-RzR1?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAB0q1vsBp4hULNTjGJX-vWVJ4DU-a38UXeY</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>urn:li:activity:7454143239860871168</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>ADIB</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>cib egypt bank abc hsbc corporate and institutional banking abu dhabi islamic bank - egypt first abu dhabi bank misr (fabmisr) hsbc private bank qnb egypt qnb group crédit agricole next bank (suisse) sa</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>Abdullah Mohamed</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>cib egypt bank abc hsbc corporate and institutional banking abu dhabi islamic bank - egypt first abu dhabi bank misr (fabmisr) hsbc private bank qnb egypt qnb group crédit agricole next bank (suisse) sa</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R54" t="n">
-        <v>53</v>
-      </c>
-      <c r="S54" t="inlineStr">
+      <c r="R56" t="n">
+        <v>55</v>
+      </c>
+      <c r="S56" t="inlineStr">
         <is>
           <t>cib egypt bank abc hsbc corporate and institutional banking abu dhabi islamic bank - egypt first abu dhabi bank misr (fa…</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
+    <row r="57">
+      <c r="A57" s="1" t="n">
         <v>71</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Luis Claudio-Jaramillo MBA, PMP, POPM</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
+      <c r="C57" s="2" t="n">
         <v>46138.64266479167</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Turning Functionality into Value 🚀
 With Abu Dhabi Islamic Bank going live as a TPP—congratulations to Mahmoud Yosry Ali  Yosry Ali and the team 👏 - we as an ecosystem are at a crossroads.
@@ -6770,108 +6994,108 @@
 And we’re only getting started.</t>
         </is>
       </c>
-      <c r="E55" t="n">
+      <c r="E57" t="n">
         <v>14</v>
       </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="inlineStr">
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/lclaudiojaramillo_turning-functionality-into-value-with-activity-7454128503471603712-GRK5?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAE4ybtUBRdwFJ0EDIJFhItHwBDR1cpnZEO0</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/lclaudiojaramillo_turning-functionality-into-value-with-activity-7454128503471603712-GRK5?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAB0q1vsBp4hULNTjGJX-vWVJ4DU-a38UXeY</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>urn:li:activity:7454128503471603712</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>ADIB</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>turning functionality into value with abu dhabi islamic bank going live as a tpp—congratulations to mahmoud yosry ali yosry ali and the team - we as an ecosystem are at a crossroads. this just the beginning. the real question is no longer what open finance enables, it’s what we choose to build with it. the standards give us the raw materials: account data across casa, cards, loans, mortgages payment capabilities from single to bulk and beyond but apis are not the story. outcomes are. we’re entering a phase where: data becomes intelligence payments become embedded experiences ai becomes the decision layer and the winners? they won’t just connect capabilities—they’ll orchestrate them into entirely new value propositions. my view: pure tpps will move fast on payments-led innovation lfis as tpps will unlock deeper value through data + ai-driven insights the real opportunity lies in: reimagining customer journeys empowering smes with smarter financial tools eliminating friction from end-to-end processes over the next 6–18 months, we won’t just see new features—we’ll see the emergence of entirely new financial experiences. this is where science meets art. this is where functionality becomes value. and we’re only getting started.</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>Luis Claudio-Jaramillo MBA, PMP, POPM</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>turning functionality into value with abu dhabi islamic bank going live as a tpp—congratulations to mahmoud yosry ali yosry ali and the team - we as an ecosystem are at a crossroads. this just the beginning. the real question is no longer what open finance enables, it’s what we choose to build with it. the standards give us the raw materials: account data across casa, cards, loans, mortgages payment capabilities from single to bulk and beyond but apis are not the story. outcomes are. we’re entering a phase where: data becomes intelligence payments become embedded experiences ai becomes the decision layer and the winners? they won’t just connect capabilities—they’ll orchestrate them into entirely new value propositions. my view: pure tpps will move fast on payments-led innovation lfis as tpps will unlock deeper value through data + ai-driven insights the real opportunity lies in: reimagining customer journeys empowering smes with smarter financial tools eliminating friction from end-to-end processes over the next 6–18 months, we won’t just see new features—we’ll see the emergence of entirely new financial experiences. this is where science meets art. this is where functionality becomes value. and we’re only getting started.</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R55" t="n">
-        <v>54</v>
-      </c>
-      <c r="S55" t="inlineStr">
+      <c r="R57" t="n">
+        <v>56</v>
+      </c>
+      <c r="S57" t="inlineStr">
         <is>
           <t>turning functionality into value with abu dhabi islamic bank going live as a tpp—congratulations to mahmoud yosry ali yosry ali and the team - we as an ecosystem are at a crossroads. • we’re entering a phase where: data becomes intelligence payments become embedded experiences ai becomes the decision layer and the winners? • the standards give us the raw materials: account data across casa, cards, loans, mortgages payment capabilities from single to bulk and beyond but apis are not the story.</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
+    <row r="58">
+      <c r="A58" s="1" t="n">
         <v>72</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Youstina Beshara</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
+      <c r="C58" s="2" t="n">
         <v>46138.62373940972</v>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>مساء الخير أنا يوستينا خريجه كليه التربيه شعبه رياضيات جامعه سوهاج وحاصله ع بكالوريوس علوم وتربيه شعبه رياضيات 
 وكمان حاصله ع دبلومه BANKER'S LOUNGE ACADEMY التأهيل للعمل المصرفي مع سفير البنوك الدكتور عماد قطارة 
@@ -6887,108 +7111,108 @@
 Vodafone</t>
         </is>
       </c>
-      <c r="E56" t="n">
-        <v>12</v>
-      </c>
-      <c r="F56" t="n">
+      <c r="E58" t="n">
+        <v>13</v>
+      </c>
+      <c r="F58" t="n">
         <v>6</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G58" t="n">
         <v>1</v>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/youstina-beshara-35bb8b3a1_%D9%85%D8%B3%D8%A7%D8%A1-%D8%A7%D9%84%D8%AE%D9%8A%D8%B1-%D8%A3%D9%86%D8%A7-%D9%8A%D9%88%D8%B3%D8%AA%D9%8A%D9%86%D8%A7-%D8%AE%D8%B1%D9%8A%D8%AC%D9%87-%D9%83%D9%84%D9%8A%D9%87-%D8%A7%D9%84%D8%AA%D8%B1%D8%A8%D9%8A%D9%87-activity-7454121645142839296-cvaK?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAE4ybtUBRdwFJ0EDIJFhItHwBDR1cpnZEO0</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/youstina-beshara-35bb8b3a1_%D9%85%D8%B3%D8%A7%D8%A1-%D8%A7%D9%84%D8%AE%D9%8A%D8%B1-%D8%A3%D9%86%D8%A7-%D9%8A%D9%88%D8%B3%D8%AA%D9%8A%D9%86%D8%A7-%D8%AE%D8%B1%D9%8A%D8%AC%D9%87-%D9%83%D9%84%D9%8A%D9%87-%D8%A7%D9%84%D8%AA%D8%B1%D8%A8%D9%8A%D9%87-activity-7454121645142839296-cvaK?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAB0q1vsBp4hULNTjGJX-vWVJ4DU-a38UXeY</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>urn:li:activity:7454121645142839296</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>ADIB</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>مساء الخير أنا يوستينا خريجه كليه التربيه شعبه رياضيات جامعه سوهاج وحاصله ع بكالوريوس علوم وتربيه شعبه رياضيات وكمان حاصله ع دبلومه banker's lounge academy التأهيل للعمل المصرفي مع سفير البنوك الدكتور عماد قطارة كنت ببحث ع وظيفه ف شركه او بنك او فرص عمل كويسه orange egypt banque misr bank abc abu dhabi islamic bank - egypt e&amp; egypt hsbc banque du caire national bank of egypt (nbe) vodafone</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>Youstina Beshara</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>مساء الخير أنا يوستينا خريجه كليه التربيه شعبه رياضيات جامعه سوهاج وحاصله ع بكالوريوس علوم وتربيه شعبه رياضيات وكمان حاصله ع دبلومه banker's lounge academy التأهيل للعمل المصرفي مع سفير البنوك الدكتور عماد قطارة كنت ببحث ع وظيفه ف شركه او بنك او فرص عمل كويسه orange egypt banque misr bank abc abu dhabi islamic bank - egypt e&amp; egypt hsbc banque du caire national bank of egypt (nbe) vodafone</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R56" t="n">
-        <v>55</v>
-      </c>
-      <c r="S56" t="inlineStr">
+      <c r="R58" t="n">
+        <v>57</v>
+      </c>
+      <c r="S58" t="inlineStr">
         <is>
           <t>مساء الخير أنا يوستينا خريجه كليه التربيه شعبه رياضيات جامعه سوهاج وحاصله ع بكالوريوس علوم وتربيه شعبه رياضيات وكمان حاص…</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
+    <row r="59">
+      <c r="A59" s="1" t="n">
         <v>73</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Mohammed Alahmed, CAMS</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
+      <c r="C59" s="2" t="n">
         <v>46138.61915790509</v>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>يسعدني مشاركة حصولي على شهادة CAMS® – إخصائي معتمد في مكافحة غسيل الأموال  
 من Association of Certified Anti-Money Laundering Specialists.  
@@ -7002,108 +7226,108 @@
 ADIB - Abu Dhabi Islamic Bank</t>
         </is>
       </c>
-      <c r="E57" t="n">
-        <v>57</v>
-      </c>
-      <c r="F57" t="n">
+      <c r="E59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F59" t="n">
         <v>18</v>
       </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="inlineStr">
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/activity-7454119984861163521-DtEN?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAE4ybtUBRdwFJ0EDIJFhItHwBDR1cpnZEO0</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/activity-7454119984861163521-DtEN?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAB0q1vsBp4hULNTjGJX-vWVJ4DU-a38UXeY</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>urn:li:activity:7454119984861163521</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>ADIB</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>يسعدني مشاركة حصولي على شهادة cams® – إخصائي معتمد في مكافحة غسيل الأموال من association of certified anti-money laundering specialists. إضافة مهمة لمسيرتي المهنية في مجال الامتثال وإدارة مخاطر الجرائم المالية. الحمد لله، وشكرًا لمصرف أبوظبي الإسلامي على دعمه المستمر. --- i’m delighted to announce that i’ve successfully obtained the cams® certification from the association of certified anti-money laundering specialists. this is a significant milestone in my journey towards mastering anti-money laundering (aml) and compliance. #cams #acams #aml #compliance adib - abu dhabi islamic bank</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>Mohammed Alahmed, CAMS</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>يسعدني مشاركة حصولي على شهادة cams® – إخصائي معتمد في مكافحة غسيل الأموال من association of certified anti-money laundering specialists. إضافة مهمة لمسيرتي المهنية في مجال الامتثال وإدارة مخاطر الجرائم المالية. الحمد لله، وشكرًا لمصرف أبوظبي الإسلامي على دعمه المستمر. --- i’m delighted to announce that i’ve successfully obtained the cams® certification from the association of certified anti-money laundering specialists. this is a significant milestone in my journey towards mastering anti-money laundering (aml) and compliance. #cams #acams #aml #compliance adib - abu dhabi islamic bank</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R57" t="n">
-        <v>56</v>
-      </c>
-      <c r="S57" t="inlineStr">
+      <c r="R59" t="n">
+        <v>58</v>
+      </c>
+      <c r="S59" t="inlineStr">
         <is>
           <t>--- i’m delighted to announce that i’ve successfully obtained the cams® certification from the association of certified anti-money laundering specialists. • يسعدني مشاركة حصولي على شهادة cams® – إخصائي معتمد في مكافحة غسيل الأموال من association of certified anti-money laundering specialists. • this is a significant milestone in my journey towards mastering anti-money laundering (aml) and compliance.</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="1" t="n">
+    <row r="60">
+      <c r="A60" s="1" t="n">
         <v>74</v>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Ghadeer khaled</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
+      <c r="C60" s="2" t="n">
         <v>46138.54963488426</v>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Celebrating the strength, resilience, and achievements of women at Abu Dhabi Islamic Bank - Egypt .
 Proud to be part of a workplace that values empowerment, inclusion, and the incredible contributions women make every day.
@@ -7111,108 +7335,108 @@
 #WomensDay #ADIB #EmpowerWomen #Inclusion #WorkplaceCulture</t>
         </is>
       </c>
-      <c r="E58" t="n">
-        <v>88</v>
-      </c>
-      <c r="F58" t="n">
+      <c r="E60" t="n">
+        <v>90</v>
+      </c>
+      <c r="F60" t="n">
         <v>2</v>
       </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="inlineStr">
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/ghadeer-khaled-5a2bb216b_womensday-adib-empowerwomen-activity-7454094790561787905-9TUk?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAE4ybtUBRdwFJ0EDIJFhItHwBDR1cpnZEO0</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/ghadeer-khaled-5a2bb216b_womensday-adib-empowerwomen-activity-7454094790561787905-9TUk?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAB0q1vsBp4hULNTjGJX-vWVJ4DU-a38UXeY</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>urn:li:activity:7454094790561787905</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>ADIB</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>celebrating the strength, resilience, and achievements of women at abu dhabi islamic bank - egypt . proud to be part of a workplace that values empowerment, inclusion, and the incredible contributions women make every day. here’s to inspiring change, breaking barriers, and continuing to support one another toward greater success. #womensday #adib #empowerwomen #inclusion #workplaceculture</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>Ghadeer khaled</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>celebrating the strength, resilience, and achievements of women at abu dhabi islamic bank - egypt . proud to be part of a workplace that values empowerment, inclusion, and the incredible contributions women make every day. here’s to inspiring change, breaking barriers, and continuing to support one another toward greater success. #womensday #adib #empowerwomen #inclusion #workplaceculture</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R58" t="n">
-        <v>57</v>
-      </c>
-      <c r="S58" t="inlineStr">
+      <c r="R60" t="n">
+        <v>59</v>
+      </c>
+      <c r="S60" t="inlineStr">
         <is>
           <t>proud to be part of a workplace that values empowerment, inclusion, and the incredible contributions women make every day. • here’s to inspiring change, breaking barriers, and continuing to support one another toward greater success. • celebrating the strength, resilience, and achievements of women at abu dhabi islamic bank - egypt .</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
+    <row r="61">
+      <c r="A61" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>youssef Muhammed</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
+      <c r="C61" s="2" t="n">
         <v>46138.52233572917</v>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>ابحث عن فرصة في ادارات في بنوك مع العلم لدي خبرة في مجال البنوك 
 لو حد يعرف يساعد وجزاكم الله خيرا 💗 
@@ -7226,108 +7450,108 @@
 @bank</t>
         </is>
       </c>
-      <c r="E59" t="n">
+      <c r="E61" t="n">
         <v>2</v>
       </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="inlineStr">
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr">
         <is>
           <t>document</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/youssef-muhammed-3569262a6_cv-activity-7454084897679269888-1-4p?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAE4ybtUBRdwFJ0EDIJFhItHwBDR1cpnZEO0</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/youssef-muhammed-3569262a6_cv-activity-7454084897679269888-1-4p?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAB0q1vsBp4hULNTjGJX-vWVJ4DU-a38UXeY</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>urn:li:activity:7454084897679269888</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>ADIB</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>ابحث عن فرصة في ادارات في بنوك مع العلم لدي خبرة في مجال البنوك لو حد يعرف يساعد وجزاكم الله خيرا qnb egypt cib egypt alexbank national bank of egypt (nbe) abu dhabi islamic bank - egypt bank abc en algérie hsbc international wealth and premier banking @bank</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>youssef Muhammed</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>ابحث عن فرصة في ادارات في بنوك مع العلم لدي خبرة في مجال البنوك لو حد يعرف يساعد وجزاكم الله خيرا qnb egypt cib egypt alexbank national bank of egypt (nbe) abu dhabi islamic bank - egypt bank abc en algérie hsbc international wealth and premier banking @bank</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R59" t="n">
-        <v>58</v>
-      </c>
-      <c r="S59" t="inlineStr">
+      <c r="R61" t="n">
+        <v>60</v>
+      </c>
+      <c r="S61" t="inlineStr">
         <is>
           <t>ابحث عن فرصة في ادارات في بنوك مع العلم لدي خبرة في مجال البنوك لو حد يعرف يساعد وجزاكم الله خيرا qnb egypt cib egypt al…</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>5. Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>Abu Dhabi Islamic Bank (ADIB)</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
+    <row r="62">
+      <c r="A62" s="1" t="n">
         <v>81</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Aditya Roshan</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
+      <c r="C62" s="2" t="n">
         <v>46138.40764421297</v>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Commercial Bank of Dubai reporting ~Dh830M net profit in Q1 reflects steady performance backed by core banking fundamentals.
 → Operating income up ~6% YoY
@@ -7342,215 +7566,215 @@
 Commercial Bank of Dubai Khaleej Times</t>
         </is>
       </c>
-      <c r="E60" t="n">
+      <c r="E62" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" t="n">
         <v>2</v>
       </c>
-      <c r="F60" t="n">
-        <v>2</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="inlineStr">
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>article</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/roshanaditya_commercial-bank-of-dubai-q1-net-profit-hits-activity-7454043334865543168-C9yT?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEsbscwB4exxXLT9qmMHDRY039o5JTp8myQ</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/roshanaditya_commercial-bank-of-dubai-q1-net-profit-hits-activity-7454043334865543168-C9yT?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAC_ifSIBLNKN-CYmgkfIGEtul2vGCEXomr8</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>urn:li:activity:7454043334865543168</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>CBD</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>commercial bank of dubai reporting ~dh830m net profit in q1 reflects steady performance backed by core banking fundamentals. → operating income up ~6% yoy → net interest income supported by higher loan volumes → non-interest income contributing to overall growth → continued focus on disciplined cost and risk management what stands out is the stability. even in mixed conditions, performance remains consistent — supported by balanced income streams and controlled risk. because in banking, sustained results aren’t just about growth. they’re about how well fundamentals hold over time. #uae #banking #fintech #growth #strategy commercial bank of dubai khaleej times</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>Aditya Roshan</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>commercial bank of dubai reporting ~dh830m net profit in q1 reflects steady performance backed by core banking fundamentals. → operating income up ~6% yoy → net interest income supported by higher loan volumes → non-interest income contributing to overall growth → continued focus on disciplined cost and risk management what stands out is the stability. even in mixed conditions, performance remains consistent — supported by balanced income streams and controlled risk. because in banking, sustained results aren’t just about growth. they’re about how well fundamentals hold over time. #uae #banking #fintech #growth #strategy commercial bank of dubai khaleej times</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R60" t="n">
-        <v>59</v>
-      </c>
-      <c r="S60" t="inlineStr">
+      <c r="R62" t="n">
+        <v>61</v>
+      </c>
+      <c r="S62" t="inlineStr">
         <is>
           <t>commercial bank of dubai reporting ~dh830m net profit in q1 reflects steady performance backed by core banking fundamentals. • even in mixed conditions, performance remains consistent — supported by balanced income streams and controlled risk. • #uae #banking #fintech #growth #strategy commercial bank of dubai khaleej times</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>6. Commercial Bank of Dubai (CBD)</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>Commercial Bank of Dubai (CBD)</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
+    <row r="63">
+      <c r="A63" s="1" t="n">
         <v>83</v>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Nizar Bouzeliffa</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
+      <c r="C63" s="2" t="n">
         <v>46138.40124899305</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Made by CreatedNow.
 First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
-      <c r="E61" t="n">
+      <c r="E63" t="n">
         <v>1</v>
       </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="inlineStr">
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/bouzeliffanizar_fab-activity-7454041017315520512-YZGM?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAF0xL_oByCbKvMWnw2gqp5d9JJD_HZczzDg</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/bouzeliffanizar_fab-activity-7454041017315520512-YZGM?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADIsm-sBDLgBfGf9vFksAqOJsqyCiIPXOkw</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>urn:li:activity:7454041017315520512</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>FAB</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>made by creatednow. first abu dhabi bank (fab)</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>Nizar Bouzeliffa</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>made by creatednow. first abu dhabi bank (fab)</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R61" t="n">
-        <v>60</v>
-      </c>
-      <c r="S61" t="inlineStr">
+      <c r="R63" t="n">
+        <v>62</v>
+      </c>
+      <c r="S63" t="inlineStr">
         <is>
           <t>first abu dhabi bank (fab)</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>3. First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>86</v>
-      </c>
-      <c r="B62" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>Kamal Elzohery</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
+      <c r="C64" s="2" t="n">
         <v>46138.72050105324</v>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>انا خبره في real estate اكتر من ٨سنوات وبدور علي فرصه داخل بنك في قسم التمويل العقاري 
 Strong experience in client communication and closing meetings
@@ -7567,435 +7791,435 @@
 @bank</t>
         </is>
       </c>
-      <c r="E62" t="n">
+      <c r="E64" t="n">
         <v>1</v>
       </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="inlineStr">
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/kamal-elzohery-689449368_%D8%A7%D9%86%D8%A7-%D8%AE%D8%A8%D8%B1%D9%87-%D9%81%D9%8A-real-estate-%D8%A7%D9%83%D8%AA%D8%B1-%D9%85%D9%86-%D9%A8%D8%B3%D9%86%D9%88%D8%A7%D8%AA-%D9%88%D8%A8%D8%AF%D9%88%D8%B1-activity-7454156710388166656-YfaO?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFtpU50B30XLLMtDrBfvxuEmy1aFP99wtqQ</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/kamal-elzohery-689449368_%D8%A7%D9%86%D8%A7-%D8%AE%D8%A8%D8%B1%D9%87-%D9%81%D9%8A-real-estate-%D8%A7%D9%83%D8%AA%D8%B1-%D9%85%D9%86-%D9%A8%D8%B3%D9%86%D9%88%D8%A7%D8%AA-%D9%88%D8%A8%D8%AF%D9%88%D8%B1-activity-7454156710388166656-YfaO?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACFDgJABcV1EsFW9GKPUUjY2gWBSxjiEQU4</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>urn:li:activity:7454156710388166656</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>FAB</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>انا خبره في real estate اكتر من ٨سنوات وبدور علي فرصه داخل بنك في قسم التمويل العقاري strong experience in client communication and closing meetings skilled in managing client interactions and successfully closing deals proven ability to build relationships with clients and close meetings effectively بنك البلاد | bank albilad first bank egypt first abu dhabi bank misr (fabmisr) bank abc en algérie deutsche bank investment bank al ahly sabbour developments hsbc corporate and institutional banking banque misr @bank</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>Kamal Elzohery</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>انا خبره في real estate اكتر من ٨سنوات وبدور علي فرصه داخل بنك في قسم التمويل العقاري strong experience in client communication and closing meetings skilled in managing client interactions and successfully closing deals proven ability to build relationships with clients and close meetings effectively بنك البلاد | bank albilad first bank egypt first abu dhabi bank misr (fabmisr) bank abc en algérie deutsche bank investment bank al ahly sabbour developments hsbc corporate and institutional banking banque misr @bank</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R62" t="n">
-        <v>61</v>
-      </c>
-      <c r="S62" t="inlineStr">
+      <c r="R64" t="n">
+        <v>63</v>
+      </c>
+      <c r="S64" t="inlineStr">
         <is>
           <t>انا خبره في real estate اكتر من ٨سنوات وبدور علي فرصه داخل بنك في قسم التمويل العقاري strong experience in client commun…</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>3. First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="B63" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B65" t="inlineStr">
         <is>
           <t>Qaisar Al Balushi</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n">
+      <c r="C65" s="2" t="n">
         <v>46138.70083388889</v>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>As I leave FAB after nearly five wonderful years, I do so with sincere gratitude for a remarkable journey filled with learning, collaboration, and growth. FAB has provided an excellent environment with an international mindset and valuable insights into technology and transformation.
 I am thankful to the organization and wish First Abu Dhabi Bank (FAB) continued success. Special thanks to Ali Al-Lawati and Dima AlKarmy — true leaders whose support and guidance I deeply value.
 To my team, you will be missed. Thank you for the shared achievements and memories.</t>
         </is>
       </c>
-      <c r="E63" t="n">
-        <v>97</v>
-      </c>
-      <c r="F63" t="n">
-        <v>33</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="inlineStr">
+      <c r="E65" t="n">
+        <v>99</v>
+      </c>
+      <c r="F65" t="n">
+        <v>36</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/qaisar-al-balushi-76320453_as-i-leave-fab-after-nearly-five-wonderful-activity-7454149583246594048-bc4K?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFtpU50B30XLLMtDrBfvxuEmy1aFP99wtqQ</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/qaisar-al-balushi-76320453_as-i-leave-fab-after-nearly-five-wonderful-activity-7454149583246594048-bc4K?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACFDgJABcV1EsFW9GKPUUjY2gWBSxjiEQU4</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>urn:li:activity:7454149583246594048</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>FAB</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>as i leave fab after nearly five wonderful years, i do so with sincere gratitude for a remarkable journey filled with learning, collaboration, and growth. fab has provided an excellent environment with an international mindset and valuable insights into technology and transformation. i am thankful to the organization and wish first abu dhabi bank (fab) continued success. special thanks to ali al-lawati and dima alkarmy — true leaders whose support and guidance i deeply value. to my team, you will be missed. thank you for the shared achievements and memories.</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>Qaisar Al Balushi</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>as i leave fab after nearly five wonderful years, i do so with sincere gratitude for a remarkable journey filled with learning, collaboration, and growth. fab has provided an excellent environment with an international mindset and valuable insights into technology and transformation. i am thankful to the organization and wish first abu dhabi bank (fab) continued success. special thanks to ali al-lawati and dima alkarmy — true leaders whose support and guidance i deeply value. to my team, you will be missed. thank you for the shared achievements and memories.</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R63" t="n">
-        <v>62</v>
-      </c>
-      <c r="S63" t="inlineStr">
+      <c r="R65" t="n">
+        <v>64</v>
+      </c>
+      <c r="S65" t="inlineStr">
         <is>
           <t>as i leave fab after nearly five wonderful years, i do so with sincere gratitude for a remarkable journey filled with learning, collaboration, and growth. • fab has provided an excellent environment with an international mindset and valuable insights into technology and transformation. • special thanks to ali al-lawati and dima alkarmy — true leaders whose support and guidance i deeply value.</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>3. First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="B64" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B66" t="inlineStr">
         <is>
           <t>Tradearabia</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
+      <c r="C66" s="2" t="n">
         <v>46138.62506332176</v>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>First Abu Dhabi Bank (FAB), one of the world’s largest financial institutions, said its operating income increased by 6% yoy to AED9.34 billion ($2.54 billion) for the first quarter of 2026, while operating profit rose by 5% yoy to AED7.22 billion ($1.97 billion). 
 Read more on https://lnkd.in/d3UFcsj6
 #Tradearabia #bank #abudhabi #finance</t>
         </is>
       </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="inlineStr">
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>980</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/tradearabiaonline_tradearabia-bank-abudhabi-activity-7454122124912336896-XQw6?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFtpU50B30XLLMtDrBfvxuEmy1aFP99wtqQ</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/tradearabiaonline_tradearabia-bank-abudhabi-activity-7454122124912336896-XQw6?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACFDgJABcV1EsFW9GKPUUjY2gWBSxjiEQU4</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>urn:li:activity:7454122124912336896</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>FAB</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>first abu dhabi bank (fab), one of the world’s largest financial institutions, said its operating income increased by 6% yoy to aed9.34 billion ($2.54 billion) for the first quarter of 2026, while operating profit rose by 5% yoy to aed7.22 billion ($1.97 billion). read more on  #tradearabia #bank #abudhabi #finance</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>Tradearabia</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>first abu dhabi bank (fab), one of the world’s largest financial institutions, said its operating income increased by 6% yoy to aed9.34 billion ($2.54 billion) for the first quarter of 2026, while operating profit rose by 5% yoy to aed7.22 billion ($1.97 billion). read more on  #tradearabia #bank #abudhabi #finance</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R64" t="n">
-        <v>63</v>
-      </c>
-      <c r="S64" t="inlineStr">
+      <c r="R66" t="n">
+        <v>65</v>
+      </c>
+      <c r="S66" t="inlineStr">
         <is>
           <t>read more on #tradearabia #bank #abudhabi #finance</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="V66" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>3. First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="B65" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>Mansuor Alessa ‘Cert CII</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
+      <c r="C67" s="2" t="n">
         <v>46138.62282017361</v>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>First Abu Dhabi Bank (FAB) 🇸🇦Director, Securities Services-
 • FAB Capital (#Riyadh)</t>
         </is>
       </c>
-      <c r="E65" t="n">
+      <c r="E67" t="n">
         <v>2</v>
       </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="inlineStr">
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/activity-7454121312022609920-32wY?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFtpU50B30XLLMtDrBfvxuEmy1aFP99wtqQ</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/activity-7454121312022609920-32wY?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACFDgJABcV1EsFW9GKPUUjY2gWBSxjiEQU4</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>urn:li:activity:7454121312022609920</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>FAB</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>first abu dhabi bank (fab) director, securities services- • fab capital (#riyadh)</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>Mansuor Alessa ‘Cert CII</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>first abu dhabi bank (fab) director, securities services- • fab capital (#riyadh)</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R65" t="n">
-        <v>64</v>
-      </c>
-      <c r="S65" t="inlineStr">
+      <c r="R67" t="n">
+        <v>66</v>
+      </c>
+      <c r="S67" t="inlineStr">
         <is>
           <t>first abu dhabi bank (fab) director, securities services- • fab capital (#riyadh)</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>3. First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B66" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B68" t="inlineStr">
         <is>
           <t>Rizwan Ahmed, CSAA</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
+      <c r="C68" s="2" t="n">
         <v>46138.52262508102</v>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Vacancy, Product Owner, Mortgages.
 First Abu Dhabi Bank
@@ -8005,108 +8229,108 @@
 https://lnkd.in/dd2aEJrw</t>
         </is>
       </c>
-      <c r="E66" t="n">
+      <c r="E68" t="n">
         <v>5</v>
       </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="inlineStr">
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/rizwan-ahmed-csaa-46499735_vacancy-product-owner-mortgages-first-activity-7454085002537086976-j41b?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFtpU50B30XLLMtDrBfvxuEmy1aFP99wtqQ</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/rizwan-ahmed-csaa-46499735_vacancy-product-owner-mortgages-first-activity-7454085002537086976-j41b?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACFDgJABcV1EsFW9GKPUUjY2gWBSxjiEQU4</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>urn:li:activity:7454085002537086976</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>FAB</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>vacancy, product owner, mortgages. first abu dhabi bank uae onsite full-time</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>Rizwan Ahmed, CSAA</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>vacancy, product owner, mortgages. first abu dhabi bank uae onsite full-time</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R66" t="n">
-        <v>65</v>
-      </c>
-      <c r="S66" t="inlineStr">
+      <c r="R68" t="n">
+        <v>67</v>
+      </c>
+      <c r="S68" t="inlineStr">
         <is>
           <t>first abu dhabi bank uae onsite full-time • vacancy, product owner, mortgages.</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>3. First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="B67" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B69" t="inlineStr">
         <is>
           <t>UAE Administration &amp; Human Resources Community</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
+      <c r="C69" s="2" t="n">
         <v>46138.51858108796</v>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>First Abu Dhabi Bank (FAB) is Looking for 
 - Executive Director
@@ -8116,94 +8340,94 @@
 https://lnkd.in/esQGVz9j</t>
         </is>
       </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="inlineStr">
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="inlineStr">
         <is>
           <t>article</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>763</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/administration-human-resources-community_first-abu-dhabi-bank-fab-activity-7454083537042898944-XvUb?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFtpU50B30XLLMtDrBfvxuEmy1aFP99wtqQ</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/administration-human-resources-community_first-abu-dhabi-bank-fab-activity-7454083537042898944-XvUb?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACFDgJABcV1EsFW9GKPUUjY2gWBSxjiEQU4</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>urn:li:activity:7454083537042898944</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>FAB</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>first abu dhabi bank (fab) is looking for - executive director - sales executive - executive director – sales - avp, digital &amp; social media</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>UAE Administration &amp; Human Resources Community</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>first abu dhabi bank (fab) is looking for - executive director - sales executive - executive director – sales - avp, digital &amp; social media</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R67" t="n">
-        <v>66</v>
-      </c>
-      <c r="S67" t="inlineStr">
+      <c r="R69" t="n">
+        <v>68</v>
+      </c>
+      <c r="S69" t="inlineStr">
         <is>
           <t>first abu dhabi bank (fab) is looking for - executive director - sales executive - executive director – sales - avp, digital &amp; social media</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>26-04-2026</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="V69" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>3. First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>First Abu Dhabi Bank (FAB)</t>
         </is>
